--- a/research/traditional_assets/database/data/barbados/barbados_computer_services.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_computer_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1748794782444227</v>
+        <v>0.1748258195313882</v>
       </c>
       <c r="C2">
-        <v>545.0582615196419</v>
+        <v>540.6691706616417</v>
       </c>
       <c r="D2">
-        <v>514.3582615196418</v>
+        <v>514.5721706616416</v>
       </c>
       <c r="E2">
-        <v>-187.4</v>
+        <v>-182.797</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.603</v>
       </c>
       <c r="G2">
         <v>30.7</v>
@@ -1451,28 +1451,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2315309</v>
       </c>
       <c r="N2">
-        <v>43.13333333333333</v>
+        <v>42.90180243333333</v>
       </c>
       <c r="O2">
-        <v>2.372333333333333</v>
+        <v>2.359599133833333</v>
       </c>
       <c r="P2">
-        <v>40.761</v>
+        <v>40.5422032995</v>
       </c>
       <c r="Q2">
-        <v>52.161</v>
+        <v>51.94220329949999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1748794782444227</v>
+        <v>0.1761116005367558</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763958</v>
+        <v>1.001759991307034</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>186.2962279908787</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1748258195313882</v>
+        <v>0.1747721608183538</v>
       </c>
       <c r="C3">
-        <v>540.6691706616417</v>
+        <v>536.2802577969261</v>
       </c>
       <c r="D3">
-        <v>514.5721706616416</v>
+        <v>514.7862577969261</v>
       </c>
       <c r="E3">
-        <v>-182.797</v>
+        <v>-178.194</v>
       </c>
       <c r="F3">
-        <v>4.603</v>
+        <v>9.206</v>
       </c>
       <c r="G3">
         <v>30.7</v>
@@ -1533,28 +1533,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M3">
-        <v>0.2315309</v>
+        <v>0.4630618</v>
       </c>
       <c r="N3">
-        <v>42.90180243333333</v>
+        <v>42.67027153333333</v>
       </c>
       <c r="O3">
-        <v>2.359599133833333</v>
+        <v>2.346864934333333</v>
       </c>
       <c r="P3">
-        <v>40.5422032995</v>
+        <v>40.323406599</v>
       </c>
       <c r="Q3">
-        <v>51.94220329949999</v>
+        <v>51.723406599</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1761116005367558</v>
+        <v>0.1773688681819937</v>
       </c>
       <c r="T3">
-        <v>1.001759991307034</v>
+        <v>1.011425135624012</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.2962279908787</v>
+        <v>93.14811399543935</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1747721608183538</v>
+        <v>0.1747185021053194</v>
       </c>
       <c r="C4">
-        <v>536.2802577969261</v>
+        <v>531.8915231477492</v>
       </c>
       <c r="D4">
-        <v>514.7862577969261</v>
+        <v>515.0005231477492</v>
       </c>
       <c r="E4">
-        <v>-178.194</v>
+        <v>-173.591</v>
       </c>
       <c r="F4">
-        <v>9.206</v>
+        <v>13.809</v>
       </c>
       <c r="G4">
         <v>30.7</v>
@@ -1615,28 +1615,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M4">
-        <v>0.4630618</v>
+        <v>0.6945926999999998</v>
       </c>
       <c r="N4">
-        <v>42.67027153333333</v>
+        <v>42.43874063333333</v>
       </c>
       <c r="O4">
-        <v>2.346864934333333</v>
+        <v>2.334130734833333</v>
       </c>
       <c r="P4">
-        <v>40.323406599</v>
+        <v>40.1046098985</v>
       </c>
       <c r="Q4">
-        <v>51.723406599</v>
+        <v>51.5046098985</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1773688681819937</v>
+        <v>0.1786520588714633</v>
       </c>
       <c r="T4">
-        <v>1.011425135624012</v>
+        <v>1.021289561267113</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.14811399543935</v>
+        <v>62.09874266362624</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1747185021053194</v>
+        <v>0.1746648433922849</v>
       </c>
       <c r="C5">
-        <v>531.8915231477492</v>
+        <v>527.5029669367357</v>
       </c>
       <c r="D5">
-        <v>515.0005231477492</v>
+        <v>515.2149669367357</v>
       </c>
       <c r="E5">
-        <v>-173.591</v>
+        <v>-168.988</v>
       </c>
       <c r="F5">
-        <v>13.809</v>
+        <v>18.412</v>
       </c>
       <c r="G5">
         <v>30.7</v>
@@ -1697,28 +1697,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M5">
-        <v>0.6945926999999998</v>
+        <v>0.9261235999999999</v>
       </c>
       <c r="N5">
-        <v>42.43874063333333</v>
+        <v>42.20720973333334</v>
       </c>
       <c r="O5">
-        <v>2.334130734833333</v>
+        <v>2.321396535333334</v>
       </c>
       <c r="P5">
-        <v>40.1046098985</v>
+        <v>39.885813198</v>
       </c>
       <c r="Q5">
-        <v>51.5046098985</v>
+        <v>51.285813198</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1786520588714633</v>
+        <v>0.1799619827002968</v>
       </c>
       <c r="T5">
-        <v>1.021289561267113</v>
+        <v>1.031359495777779</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.09874266362624</v>
+        <v>46.57405699771968</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1746648433922849</v>
+        <v>0.1746111846792505</v>
       </c>
       <c r="C6">
-        <v>527.5029669367357</v>
+        <v>523.1145893868803</v>
       </c>
       <c r="D6">
-        <v>515.2149669367357</v>
+        <v>515.4295893868803</v>
       </c>
       <c r="E6">
-        <v>-168.988</v>
+        <v>-164.385</v>
       </c>
       <c r="F6">
-        <v>18.412</v>
+        <v>23.015</v>
       </c>
       <c r="G6">
         <v>30.7</v>
@@ -1779,28 +1779,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M6">
-        <v>0.9261235999999999</v>
+        <v>1.1576545</v>
       </c>
       <c r="N6">
-        <v>42.20720973333334</v>
+        <v>41.97567883333333</v>
       </c>
       <c r="O6">
-        <v>2.321396535333334</v>
+        <v>2.308662335833333</v>
       </c>
       <c r="P6">
-        <v>39.885813198</v>
+        <v>39.6670164975</v>
       </c>
       <c r="Q6">
-        <v>51.285813198</v>
+        <v>51.0670164975</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1799619827002968</v>
+        <v>0.1812994838728953</v>
       </c>
       <c r="T6">
-        <v>1.031359495777779</v>
+        <v>1.041641428909722</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.57405699771968</v>
+        <v>37.25924559817574</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1746111846792505</v>
+        <v>0.1745575259662161</v>
       </c>
       <c r="C7">
-        <v>523.1145893868803</v>
+        <v>518.7263907215504</v>
       </c>
       <c r="D7">
-        <v>515.4295893868803</v>
+        <v>515.6443907215504</v>
       </c>
       <c r="E7">
-        <v>-164.385</v>
+        <v>-159.782</v>
       </c>
       <c r="F7">
-        <v>23.015</v>
+        <v>27.618</v>
       </c>
       <c r="G7">
         <v>30.7</v>
@@ -1861,28 +1861,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M7">
-        <v>1.1576545</v>
+        <v>1.3891854</v>
       </c>
       <c r="N7">
-        <v>41.97567883333333</v>
+        <v>41.74414793333333</v>
       </c>
       <c r="O7">
-        <v>2.308662335833333</v>
+        <v>2.295928136333333</v>
       </c>
       <c r="P7">
-        <v>39.6670164975</v>
+        <v>39.448219797</v>
       </c>
       <c r="Q7">
-        <v>51.0670164975</v>
+        <v>50.848219797</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1812994838728953</v>
+        <v>0.1826654425172512</v>
       </c>
       <c r="T7">
-        <v>1.041641428909722</v>
+        <v>1.052142126576387</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.25924559817574</v>
+        <v>31.04937133181311</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1745575259662161</v>
+        <v>0.1745038672531816</v>
       </c>
       <c r="C8">
-        <v>518.7263907215504</v>
+        <v>514.3383711644854</v>
       </c>
       <c r="D8">
-        <v>515.6443907215504</v>
+        <v>515.8593711644853</v>
       </c>
       <c r="E8">
-        <v>-159.782</v>
+        <v>-155.179</v>
       </c>
       <c r="F8">
-        <v>27.61799999999999</v>
+        <v>32.221</v>
       </c>
       <c r="G8">
         <v>30.7</v>
@@ -1943,28 +1943,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M8">
-        <v>1.3891854</v>
+        <v>1.6207163</v>
       </c>
       <c r="N8">
-        <v>41.74414793333333</v>
+        <v>41.51261703333333</v>
       </c>
       <c r="O8">
-        <v>2.295928136333333</v>
+        <v>2.283193936833333</v>
       </c>
       <c r="P8">
-        <v>39.448219797</v>
+        <v>39.2294230965</v>
       </c>
       <c r="Q8">
-        <v>50.848219797</v>
+        <v>50.6294230965</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1826654425172512</v>
+        <v>0.1840607766163243</v>
       </c>
       <c r="T8">
-        <v>1.052142126576387</v>
+        <v>1.062868645698249</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.04937133181312</v>
+        <v>26.61374685583982</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1745038672531816</v>
+        <v>0.1744502085401472</v>
       </c>
       <c r="C9">
-        <v>514.3383711644855</v>
+        <v>509.9505309397981</v>
       </c>
       <c r="D9">
-        <v>515.8593711644854</v>
+        <v>516.074530939798</v>
       </c>
       <c r="E9">
-        <v>-155.179</v>
+        <v>-150.576</v>
       </c>
       <c r="F9">
-        <v>32.221</v>
+        <v>36.824</v>
       </c>
       <c r="G9">
         <v>30.7</v>
@@ -2025,28 +2025,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M9">
-        <v>1.6207163</v>
+        <v>1.8522472</v>
       </c>
       <c r="N9">
-        <v>41.51261703333333</v>
+        <v>41.28108613333333</v>
       </c>
       <c r="O9">
-        <v>2.283193936833333</v>
+        <v>2.270459737333333</v>
       </c>
       <c r="P9">
-        <v>39.2294230965</v>
+        <v>39.010626396</v>
       </c>
       <c r="Q9">
-        <v>50.6294230965</v>
+        <v>50.410626396</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1840607766163243</v>
+        <v>0.1854864440653774</v>
       </c>
       <c r="T9">
-        <v>1.062868645698249</v>
+        <v>1.073828350018413</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.61374685583982</v>
+        <v>23.28702849885984</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1744502085401472</v>
+        <v>0.1743965498271128</v>
       </c>
       <c r="C10">
-        <v>509.9505309397981</v>
+        <v>505.5628702719755</v>
       </c>
       <c r="D10">
-        <v>516.074530939798</v>
+        <v>516.2898702719755</v>
       </c>
       <c r="E10">
-        <v>-150.576</v>
+        <v>-145.973</v>
       </c>
       <c r="F10">
-        <v>36.824</v>
+        <v>41.42699999999999</v>
       </c>
       <c r="G10">
         <v>30.7</v>
@@ -2107,28 +2107,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M10">
-        <v>1.8522472</v>
+        <v>2.0837781</v>
       </c>
       <c r="N10">
-        <v>41.28108613333333</v>
+        <v>41.04955523333334</v>
       </c>
       <c r="O10">
-        <v>2.270459737333333</v>
+        <v>2.257725537833334</v>
       </c>
       <c r="P10">
-        <v>39.010626396</v>
+        <v>38.79182969550001</v>
       </c>
       <c r="Q10">
-        <v>50.410626396</v>
+        <v>50.1918296955</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1854864440653774</v>
+        <v>0.1869434448649591</v>
       </c>
       <c r="T10">
-        <v>1.073828350018413</v>
+        <v>1.085028926960997</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.28702849885984</v>
+        <v>20.69958088787542</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1743965498271128</v>
+        <v>0.1743428911140783</v>
       </c>
       <c r="C11">
-        <v>505.5628702719755</v>
+        <v>501.1753893858792</v>
       </c>
       <c r="D11">
-        <v>516.2898702719755</v>
+        <v>516.5053893858791</v>
       </c>
       <c r="E11">
-        <v>-145.973</v>
+        <v>-141.37</v>
       </c>
       <c r="F11">
-        <v>41.42699999999999</v>
+        <v>46.02999999999999</v>
       </c>
       <c r="G11">
         <v>30.7</v>
@@ -2189,28 +2189,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M11">
-        <v>2.0837781</v>
+        <v>2.315309</v>
       </c>
       <c r="N11">
-        <v>41.04955523333334</v>
+        <v>40.81802433333333</v>
       </c>
       <c r="O11">
-        <v>2.257725537833334</v>
+        <v>2.244991338333334</v>
       </c>
       <c r="P11">
-        <v>38.79182969550001</v>
+        <v>38.573032995</v>
       </c>
       <c r="Q11">
-        <v>50.1918296955</v>
+        <v>49.973032995</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1869434448649591</v>
+        <v>0.1884328234600871</v>
       </c>
       <c r="T11">
-        <v>1.085028926960997</v>
+        <v>1.096478405613417</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.69958088787542</v>
+        <v>18.62962279908787</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1743428911140783</v>
+        <v>0.1742892324010439</v>
       </c>
       <c r="C12">
-        <v>501.1753893858792</v>
+        <v>496.7880885067462</v>
       </c>
       <c r="D12">
-        <v>516.5053893858791</v>
+        <v>516.7210885067461</v>
       </c>
       <c r="E12">
-        <v>-141.37</v>
+        <v>-136.767</v>
       </c>
       <c r="F12">
-        <v>46.03</v>
+        <v>50.633</v>
       </c>
       <c r="G12">
         <v>30.7</v>
@@ -2271,28 +2271,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M12">
-        <v>2.315309</v>
+        <v>2.5468399</v>
       </c>
       <c r="N12">
-        <v>40.81802433333333</v>
+        <v>40.58649343333333</v>
       </c>
       <c r="O12">
-        <v>2.244991338333334</v>
+        <v>2.232257138833333</v>
       </c>
       <c r="P12">
-        <v>38.573032995</v>
+        <v>38.3542362945</v>
       </c>
       <c r="Q12">
-        <v>49.973032995</v>
+        <v>49.7542362945</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1884328234600871</v>
+        <v>0.189955671237128</v>
       </c>
       <c r="T12">
-        <v>1.096478405613417</v>
+        <v>1.108185175920948</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.62962279908787</v>
+        <v>16.93602072644352</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1742892324010439</v>
+        <v>0.1742355736880095</v>
       </c>
       <c r="C13">
-        <v>496.7880885067462</v>
+        <v>492.4009678601906</v>
       </c>
       <c r="D13">
-        <v>516.7210885067461</v>
+        <v>516.9369678601905</v>
       </c>
       <c r="E13">
-        <v>-136.767</v>
+        <v>-132.164</v>
       </c>
       <c r="F13">
-        <v>50.633</v>
+        <v>55.23599999999999</v>
       </c>
       <c r="G13">
         <v>30.7</v>
@@ -2353,28 +2353,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M13">
-        <v>2.5468399</v>
+        <v>2.778370799999999</v>
       </c>
       <c r="N13">
-        <v>40.58649343333333</v>
+        <v>40.35496253333334</v>
       </c>
       <c r="O13">
-        <v>2.232257138833333</v>
+        <v>2.219522939333333</v>
       </c>
       <c r="P13">
-        <v>38.3542362945</v>
+        <v>38.135439594</v>
       </c>
       <c r="Q13">
-        <v>49.7542362945</v>
+        <v>49.535439594</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.189955671237128</v>
+        <v>0.1915131291909199</v>
       </c>
       <c r="T13">
-        <v>1.108185175920948</v>
+        <v>1.120158009190013</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.93602072644352</v>
+        <v>15.52468566590656</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1742355736880095</v>
+        <v>0.174181914974975</v>
       </c>
       <c r="C14">
-        <v>492.4009678601906</v>
+        <v>488.014027672203</v>
       </c>
       <c r="D14">
-        <v>516.9369678601905</v>
+        <v>517.1530276722029</v>
       </c>
       <c r="E14">
-        <v>-132.164</v>
+        <v>-127.561</v>
       </c>
       <c r="F14">
-        <v>55.23599999999999</v>
+        <v>59.839</v>
       </c>
       <c r="G14">
         <v>30.7</v>
@@ -2435,28 +2435,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M14">
-        <v>2.778370799999999</v>
+        <v>3.0099017</v>
       </c>
       <c r="N14">
-        <v>40.35496253333334</v>
+        <v>40.12343163333333</v>
       </c>
       <c r="O14">
-        <v>2.219522939333333</v>
+        <v>2.206788739833333</v>
       </c>
       <c r="P14">
-        <v>38.135439594</v>
+        <v>37.9166428935</v>
       </c>
       <c r="Q14">
-        <v>49.535439594</v>
+        <v>49.3166428935</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1915131291909199</v>
+        <v>0.1931063907758334</v>
       </c>
       <c r="T14">
-        <v>1.120158009190013</v>
+        <v>1.132406080005494</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.52468566590656</v>
+        <v>14.33047907622144</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.174181914974975</v>
+        <v>0.1741282562619406</v>
       </c>
       <c r="C15">
-        <v>488.014027672203</v>
+        <v>483.6272681691527</v>
       </c>
       <c r="D15">
-        <v>517.1530276722029</v>
+        <v>517.3692681691526</v>
       </c>
       <c r="E15">
-        <v>-127.561</v>
+        <v>-122.958</v>
       </c>
       <c r="F15">
-        <v>59.839</v>
+        <v>64.44199999999999</v>
       </c>
       <c r="G15">
         <v>30.7</v>
@@ -2517,28 +2517,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M15">
-        <v>3.0099017</v>
+        <v>3.2414326</v>
       </c>
       <c r="N15">
-        <v>40.12343163333333</v>
+        <v>39.89190073333333</v>
       </c>
       <c r="O15">
-        <v>2.206788739833333</v>
+        <v>2.194054540333333</v>
       </c>
       <c r="P15">
-        <v>37.9166428935</v>
+        <v>37.697846193</v>
       </c>
       <c r="Q15">
-        <v>49.3166428935</v>
+        <v>49.097846193</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1931063907758334</v>
+        <v>0.1947367049557449</v>
       </c>
       <c r="T15">
-        <v>1.132406080005494</v>
+        <v>1.144938989677148</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.33047907622144</v>
+        <v>13.30687342791991</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1741282562619406</v>
+        <v>0.1742872225489062</v>
       </c>
       <c r="C16">
-        <v>483.6272681691527</v>
+        <v>478.3841712792097</v>
       </c>
       <c r="D16">
-        <v>517.3692681691526</v>
+        <v>516.7291712792097</v>
       </c>
       <c r="E16">
-        <v>-122.958</v>
+        <v>-118.355</v>
       </c>
       <c r="F16">
-        <v>64.44199999999999</v>
+        <v>69.045</v>
       </c>
       <c r="G16">
         <v>30.7</v>
@@ -2599,45 +2599,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M16">
-        <v>3.2414326</v>
+        <v>3.576531</v>
       </c>
       <c r="N16">
-        <v>39.89190073333333</v>
+        <v>39.55680233333333</v>
       </c>
       <c r="O16">
-        <v>2.194054540333333</v>
+        <v>2.175624128333333</v>
       </c>
       <c r="P16">
-        <v>37.697846193</v>
+        <v>37.381178205</v>
       </c>
       <c r="Q16">
-        <v>49.097846193</v>
+        <v>48.781178205</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1947367049557449</v>
+        <v>0.1964053794693014</v>
       </c>
       <c r="T16">
-        <v>1.144938989677148</v>
+        <v>1.157766791341077</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.055</v>
       </c>
       <c r="W16">
-        <v>0.04753349999999999</v>
+        <v>0.04895099999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.30687342791991</v>
+        <v>12.06010330494363</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1742872225489062</v>
+        <v>0.1742477388358717</v>
       </c>
       <c r="C17">
-        <v>478.3841712792098</v>
+        <v>473.9400093132632</v>
       </c>
       <c r="D17">
-        <v>516.7291712792097</v>
+        <v>516.8880093132632</v>
       </c>
       <c r="E17">
-        <v>-118.355</v>
+        <v>-113.752</v>
       </c>
       <c r="F17">
-        <v>69.04499999999999</v>
+        <v>73.648</v>
       </c>
       <c r="G17">
         <v>30.7</v>
@@ -2681,28 +2681,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M17">
-        <v>3.576530999999999</v>
+        <v>3.8149664</v>
       </c>
       <c r="N17">
-        <v>39.55680233333334</v>
+        <v>39.31836693333333</v>
       </c>
       <c r="O17">
-        <v>2.175624128333334</v>
+        <v>2.162510181333333</v>
       </c>
       <c r="P17">
-        <v>37.381178205</v>
+        <v>37.155856752</v>
       </c>
       <c r="Q17">
-        <v>48.781178205</v>
+        <v>48.555856752</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1964053794693014</v>
+        <v>0.1981137843284188</v>
       </c>
       <c r="T17">
-        <v>1.157766791341077</v>
+        <v>1.170900016854147</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.06010330494363</v>
+        <v>11.30634684838465</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1742477388358717</v>
+        <v>0.1742082551228373</v>
       </c>
       <c r="C18">
-        <v>473.9400093132632</v>
+        <v>469.4959450281918</v>
       </c>
       <c r="D18">
-        <v>516.8880093132632</v>
+        <v>517.0469450281918</v>
       </c>
       <c r="E18">
-        <v>-113.752</v>
+        <v>-109.149</v>
       </c>
       <c r="F18">
-        <v>73.648</v>
+        <v>78.251</v>
       </c>
       <c r="G18">
         <v>30.7</v>
@@ -2763,28 +2763,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M18">
-        <v>3.8149664</v>
+        <v>4.0534018</v>
       </c>
       <c r="N18">
-        <v>39.31836693333333</v>
+        <v>39.07993153333333</v>
       </c>
       <c r="O18">
-        <v>2.162510181333333</v>
+        <v>2.149396234333333</v>
       </c>
       <c r="P18">
-        <v>37.155856752</v>
+        <v>36.930535299</v>
       </c>
       <c r="Q18">
-        <v>48.555856752</v>
+        <v>48.330535299</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1981137843284188</v>
+        <v>0.1998633555696835</v>
       </c>
       <c r="T18">
-        <v>1.170900016854147</v>
+        <v>1.184349705632592</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.30634684838465</v>
+        <v>10.64126762200908</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1742082551228373</v>
+        <v>0.1741687714098029</v>
       </c>
       <c r="C19">
-        <v>469.4959450281918</v>
+        <v>465.0519785141293</v>
       </c>
       <c r="D19">
-        <v>517.0469450281918</v>
+        <v>517.2059785141292</v>
       </c>
       <c r="E19">
-        <v>-109.149</v>
+        <v>-104.546</v>
       </c>
       <c r="F19">
-        <v>78.251</v>
+        <v>82.854</v>
       </c>
       <c r="G19">
         <v>30.7</v>
@@ -2845,28 +2845,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M19">
-        <v>4.0534018</v>
+        <v>4.2918372</v>
       </c>
       <c r="N19">
-        <v>39.07993153333333</v>
+        <v>38.84149613333334</v>
       </c>
       <c r="O19">
-        <v>2.149396234333333</v>
+        <v>2.136282287333334</v>
       </c>
       <c r="P19">
-        <v>36.930535299</v>
+        <v>36.70521384600001</v>
       </c>
       <c r="Q19">
-        <v>48.330535299</v>
+        <v>48.10521384600001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1998633555696835</v>
+        <v>0.2016555992802474</v>
       </c>
       <c r="T19">
-        <v>1.184349705632592</v>
+        <v>1.198127435600756</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.64126762200908</v>
+        <v>10.05008608745302</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1741687714098029</v>
+        <v>0.1744345226967684</v>
       </c>
       <c r="C20">
-        <v>465.0519785141292</v>
+        <v>459.3804616686133</v>
       </c>
       <c r="D20">
-        <v>517.2059785141291</v>
+        <v>516.1374616686132</v>
       </c>
       <c r="E20">
-        <v>-104.546</v>
+        <v>-99.94300000000001</v>
       </c>
       <c r="F20">
-        <v>82.85399999999998</v>
+        <v>87.45699999999999</v>
       </c>
       <c r="G20">
         <v>30.7</v>
@@ -2927,45 +2927,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M20">
-        <v>4.291837199999999</v>
+        <v>4.6789495</v>
       </c>
       <c r="N20">
-        <v>38.84149613333334</v>
+        <v>38.45438383333333</v>
       </c>
       <c r="O20">
-        <v>2.136282287333334</v>
+        <v>2.114991110833333</v>
       </c>
       <c r="P20">
-        <v>36.70521384600001</v>
+        <v>36.3393927225</v>
       </c>
       <c r="Q20">
-        <v>48.10521384600001</v>
+        <v>47.7393927225</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2016555992802474</v>
+        <v>0.2034920959219363</v>
       </c>
       <c r="T20">
-        <v>1.198127435600756</v>
+        <v>1.21224535643233</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.055</v>
       </c>
       <c r="W20">
-        <v>0.04895099999999999</v>
+        <v>0.0505575</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.05008608745302</v>
+        <v>9.218593475593899</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1744345226967684</v>
+        <v>0.174411103983734</v>
       </c>
       <c r="C21">
-        <v>459.3804616686133</v>
+        <v>454.8714448063575</v>
       </c>
       <c r="D21">
-        <v>516.1374616686132</v>
+        <v>516.2314448063574</v>
       </c>
       <c r="E21">
-        <v>-99.94300000000001</v>
+        <v>-95.34</v>
       </c>
       <c r="F21">
-        <v>87.45699999999999</v>
+        <v>92.06</v>
       </c>
       <c r="G21">
         <v>30.7</v>
@@ -3009,28 +3009,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M21">
-        <v>4.6789495</v>
+        <v>4.92521</v>
       </c>
       <c r="N21">
-        <v>38.45438383333333</v>
+        <v>38.20812333333333</v>
       </c>
       <c r="O21">
-        <v>2.114991110833333</v>
+        <v>2.101446783333333</v>
       </c>
       <c r="P21">
-        <v>36.3393927225</v>
+        <v>36.10667655</v>
       </c>
       <c r="Q21">
-        <v>47.7393927225</v>
+        <v>47.50667655</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2034920959219363</v>
+        <v>0.2053745049796675</v>
       </c>
       <c r="T21">
-        <v>1.21224535643233</v>
+        <v>1.226716225284694</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.218593475593899</v>
+        <v>8.757663801814203</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.174411103983734</v>
+        <v>0.1743876852706996</v>
       </c>
       <c r="C22">
-        <v>454.8714448063575</v>
+        <v>450.3624621769929</v>
       </c>
       <c r="D22">
-        <v>516.2314448063574</v>
+        <v>516.3254621769929</v>
       </c>
       <c r="E22">
-        <v>-95.34</v>
+        <v>-90.73700000000001</v>
       </c>
       <c r="F22">
-        <v>92.06</v>
+        <v>96.663</v>
       </c>
       <c r="G22">
         <v>30.7</v>
@@ -3091,28 +3091,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M22">
-        <v>4.92521</v>
+        <v>5.1714705</v>
       </c>
       <c r="N22">
-        <v>38.20812333333333</v>
+        <v>37.96186283333333</v>
       </c>
       <c r="O22">
-        <v>2.101446783333333</v>
+        <v>2.087902455833333</v>
       </c>
       <c r="P22">
-        <v>36.10667655</v>
+        <v>35.8739603775</v>
       </c>
       <c r="Q22">
-        <v>47.50667655</v>
+        <v>47.2739603775</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2053745049796675</v>
+        <v>0.2073045699629109</v>
       </c>
       <c r="T22">
-        <v>1.226716225284694</v>
+        <v>1.241553445247245</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.757663801814203</v>
+        <v>8.340632192204005</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1743876852706996</v>
+        <v>0.1743642665576652</v>
       </c>
       <c r="C23">
-        <v>450.3624621769931</v>
+        <v>445.8535137992272</v>
       </c>
       <c r="D23">
-        <v>516.325462176993</v>
+        <v>516.4195137992272</v>
       </c>
       <c r="E23">
-        <v>-90.73700000000002</v>
+        <v>-86.13400000000001</v>
       </c>
       <c r="F23">
-        <v>96.66299999999998</v>
+        <v>101.266</v>
       </c>
       <c r="G23">
         <v>30.7</v>
@@ -3173,28 +3173,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M23">
-        <v>5.171470499999999</v>
+        <v>5.417731</v>
       </c>
       <c r="N23">
-        <v>37.96186283333333</v>
+        <v>37.71560233333334</v>
       </c>
       <c r="O23">
-        <v>2.087902455833333</v>
+        <v>2.074358128333333</v>
       </c>
       <c r="P23">
-        <v>35.8739603775</v>
+        <v>35.64124420500001</v>
       </c>
       <c r="Q23">
-        <v>47.2739603775</v>
+        <v>47.04124420500001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2073045699629109</v>
+        <v>0.2092841237918784</v>
       </c>
       <c r="T23">
-        <v>1.241553445247245</v>
+        <v>1.256771106747297</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.340632192204005</v>
+        <v>7.961512547103823</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1743642665576652</v>
+        <v>0.1743408478446307</v>
       </c>
       <c r="C24">
-        <v>445.8535137992272</v>
+        <v>441.3445996917809</v>
       </c>
       <c r="D24">
-        <v>516.4195137992272</v>
+        <v>516.5135996917809</v>
       </c>
       <c r="E24">
-        <v>-86.13400000000001</v>
+        <v>-81.53100000000001</v>
       </c>
       <c r="F24">
-        <v>101.266</v>
+        <v>105.869</v>
       </c>
       <c r="G24">
         <v>30.7</v>
@@ -3255,28 +3255,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M24">
-        <v>5.417731</v>
+        <v>5.6639915</v>
       </c>
       <c r="N24">
-        <v>37.71560233333334</v>
+        <v>37.46934183333333</v>
       </c>
       <c r="O24">
-        <v>2.074358128333333</v>
+        <v>2.060813800833333</v>
       </c>
       <c r="P24">
-        <v>35.64124420500001</v>
+        <v>35.4085280325</v>
       </c>
       <c r="Q24">
-        <v>47.04124420500001</v>
+        <v>46.8085280325</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2092841237918784</v>
+        <v>0.2113150946034165</v>
       </c>
       <c r="T24">
-        <v>1.256771106747297</v>
+        <v>1.272384032182415</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.961512547103823</v>
+        <v>7.615359827664524</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1743408478446307</v>
+        <v>0.1744988691315963</v>
       </c>
       <c r="C25">
-        <v>441.3445996917809</v>
+        <v>436.10740496801</v>
       </c>
       <c r="D25">
-        <v>516.5135996917809</v>
+        <v>515.8794049680099</v>
       </c>
       <c r="E25">
-        <v>-81.53100000000001</v>
+        <v>-76.92800000000001</v>
       </c>
       <c r="F25">
-        <v>105.869</v>
+        <v>110.472</v>
       </c>
       <c r="G25">
         <v>30.7</v>
@@ -3337,45 +3337,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M25">
-        <v>5.6639915</v>
+        <v>5.9986296</v>
       </c>
       <c r="N25">
-        <v>37.46934183333333</v>
+        <v>37.13470373333333</v>
       </c>
       <c r="O25">
-        <v>2.060813800833333</v>
+        <v>2.042408705333333</v>
       </c>
       <c r="P25">
-        <v>35.4085280325</v>
+        <v>35.092295028</v>
       </c>
       <c r="Q25">
-        <v>46.8085280325</v>
+        <v>46.49229502799999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2113150946034165</v>
+        <v>0.2133995120152583</v>
       </c>
       <c r="T25">
-        <v>1.272384032182415</v>
+        <v>1.288407824076352</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.055</v>
       </c>
       <c r="W25">
-        <v>0.0505575</v>
+        <v>0.0513135</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.615359827664524</v>
+        <v>7.190531206216388</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1744988691315963</v>
+        <v>0.1744830104185619</v>
       </c>
       <c r="C26">
-        <v>436.10740496801</v>
+        <v>431.5679812195846</v>
       </c>
       <c r="D26">
-        <v>515.8794049680099</v>
+        <v>515.9429812195846</v>
       </c>
       <c r="E26">
-        <v>-76.92800000000003</v>
+        <v>-72.32500000000002</v>
       </c>
       <c r="F26">
-        <v>110.472</v>
+        <v>115.075</v>
       </c>
       <c r="G26">
         <v>30.7</v>
@@ -3419,28 +3419,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M26">
-        <v>5.998629599999999</v>
+        <v>6.2485725</v>
       </c>
       <c r="N26">
-        <v>37.13470373333333</v>
+        <v>36.88476083333333</v>
       </c>
       <c r="O26">
-        <v>2.042408705333333</v>
+        <v>2.028661845833333</v>
       </c>
       <c r="P26">
-        <v>35.092295028</v>
+        <v>34.8560989875</v>
       </c>
       <c r="Q26">
-        <v>46.49229502799999</v>
+        <v>46.2560989875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2133995120152583</v>
+        <v>0.2155395138914158</v>
       </c>
       <c r="T26">
-        <v>1.288407824076352</v>
+        <v>1.30485891708746</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.190531206216389</v>
+        <v>6.902909957967733</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1744830104185619</v>
+        <v>0.1744671517055274</v>
       </c>
       <c r="C27">
-        <v>431.5679812195846</v>
+        <v>427.0285731431865</v>
       </c>
       <c r="D27">
-        <v>515.9429812195846</v>
+        <v>516.0065731431864</v>
       </c>
       <c r="E27">
-        <v>-72.32500000000002</v>
+        <v>-67.72200000000001</v>
       </c>
       <c r="F27">
-        <v>115.075</v>
+        <v>119.678</v>
       </c>
       <c r="G27">
         <v>30.7</v>
@@ -3501,28 +3501,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M27">
-        <v>6.2485725</v>
+        <v>6.4985154</v>
       </c>
       <c r="N27">
-        <v>36.88476083333333</v>
+        <v>36.63481793333333</v>
       </c>
       <c r="O27">
-        <v>2.028661845833333</v>
+        <v>2.014914986333333</v>
       </c>
       <c r="P27">
-        <v>34.8560989875</v>
+        <v>34.619902947</v>
       </c>
       <c r="Q27">
-        <v>46.2560989875</v>
+        <v>46.019902947</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2155395138914158</v>
+        <v>0.2177373536561181</v>
       </c>
       <c r="T27">
-        <v>1.30485891708746</v>
+        <v>1.321754634234004</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.902909957967733</v>
+        <v>6.637413421122821</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1744671517055274</v>
+        <v>0.174451292992493</v>
       </c>
       <c r="C28">
-        <v>427.0285731431865</v>
+        <v>422.4891807446105</v>
       </c>
       <c r="D28">
-        <v>516.0065731431864</v>
+        <v>516.0701807446104</v>
       </c>
       <c r="E28">
-        <v>-67.72200000000001</v>
+        <v>-63.11900000000001</v>
       </c>
       <c r="F28">
-        <v>119.678</v>
+        <v>124.281</v>
       </c>
       <c r="G28">
         <v>30.7</v>
@@ -3583,28 +3583,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M28">
-        <v>6.4985154</v>
+        <v>6.748458299999999</v>
       </c>
       <c r="N28">
-        <v>36.63481793333333</v>
+        <v>36.38487503333333</v>
       </c>
       <c r="O28">
-        <v>2.014914986333333</v>
+        <v>2.001168126833333</v>
       </c>
       <c r="P28">
-        <v>34.619902947</v>
+        <v>34.3837069065</v>
       </c>
       <c r="Q28">
-        <v>46.019902947</v>
+        <v>45.78370690649999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2177373536561181</v>
+        <v>0.2199954082088945</v>
       </c>
       <c r="T28">
-        <v>1.321754634234004</v>
+        <v>1.339113247740728</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.637413421122821</v>
+        <v>6.391583294414568</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.174451292992493</v>
+        <v>0.1744354342794585</v>
       </c>
       <c r="C29">
-        <v>422.4891807446105</v>
+        <v>417.9498040296555</v>
       </c>
       <c r="D29">
-        <v>516.0701807446104</v>
+        <v>516.1338040296555</v>
       </c>
       <c r="E29">
-        <v>-63.11900000000001</v>
+        <v>-58.51600000000002</v>
       </c>
       <c r="F29">
-        <v>124.281</v>
+        <v>128.884</v>
       </c>
       <c r="G29">
         <v>30.7</v>
@@ -3665,28 +3665,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M29">
-        <v>6.748458299999999</v>
+        <v>6.998401199999999</v>
       </c>
       <c r="N29">
-        <v>36.38487503333333</v>
+        <v>36.13493213333334</v>
       </c>
       <c r="O29">
-        <v>2.001168126833333</v>
+        <v>1.987421267333334</v>
       </c>
       <c r="P29">
-        <v>34.3837069065</v>
+        <v>34.147510866</v>
       </c>
       <c r="Q29">
-        <v>45.78370690649999</v>
+        <v>45.547510866</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2199954082088945</v>
+        <v>0.222316186499248</v>
       </c>
       <c r="T29">
-        <v>1.339113247740728</v>
+        <v>1.356954044955971</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.391583294414568</v>
+        <v>6.163312462471191</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1744354342794585</v>
+        <v>0.1746936255664241</v>
       </c>
       <c r="C30">
-        <v>417.9498040296555</v>
+        <v>412.3129185250525</v>
       </c>
       <c r="D30">
-        <v>516.1338040296555</v>
+        <v>515.0999185250524</v>
       </c>
       <c r="E30">
-        <v>-58.51600000000002</v>
+        <v>-53.91300000000001</v>
       </c>
       <c r="F30">
-        <v>128.884</v>
+        <v>133.487</v>
       </c>
       <c r="G30">
         <v>30.7</v>
@@ -3747,45 +3747,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M30">
-        <v>6.998401199999999</v>
+        <v>7.3818311</v>
       </c>
       <c r="N30">
-        <v>36.13493213333334</v>
+        <v>35.75150223333333</v>
       </c>
       <c r="O30">
-        <v>1.987421267333334</v>
+        <v>1.966332622833333</v>
       </c>
       <c r="P30">
-        <v>34.147510866</v>
+        <v>33.7851696105</v>
       </c>
       <c r="Q30">
-        <v>45.547510866</v>
+        <v>45.1851696105</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.222316186499248</v>
+        <v>0.2247023388259495</v>
       </c>
       <c r="T30">
-        <v>1.356954044955971</v>
+        <v>1.37529739983925</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.055</v>
       </c>
       <c r="W30">
-        <v>0.0513135</v>
+        <v>0.0522585</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.163312462471191</v>
+        <v>5.843175324525284</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1746936255664241</v>
+        <v>0.1746872168533897</v>
       </c>
       <c r="C31">
-        <v>412.3129185250525</v>
+        <v>407.7355310539168</v>
       </c>
       <c r="D31">
-        <v>515.0999185250524</v>
+        <v>515.1255310539167</v>
       </c>
       <c r="E31">
-        <v>-53.91300000000004</v>
+        <v>-49.31000000000003</v>
       </c>
       <c r="F31">
-        <v>133.487</v>
+        <v>138.09</v>
       </c>
       <c r="G31">
         <v>30.7</v>
@@ -3829,28 +3829,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M31">
-        <v>7.381831099999999</v>
+        <v>7.636376999999999</v>
       </c>
       <c r="N31">
-        <v>35.75150223333333</v>
+        <v>35.49695633333334</v>
       </c>
       <c r="O31">
-        <v>1.966332622833333</v>
+        <v>1.952332598333334</v>
       </c>
       <c r="P31">
-        <v>33.7851696105</v>
+        <v>33.544623735</v>
       </c>
       <c r="Q31">
-        <v>45.1851696105</v>
+        <v>44.944623735</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2247023388259495</v>
+        <v>0.2271566669334139</v>
       </c>
       <c r="T31">
-        <v>1.37529739983925</v>
+        <v>1.394164850576336</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.843175324525284</v>
+        <v>5.648402813707776</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1746872168533897</v>
+        <v>0.1746808081403553</v>
       </c>
       <c r="C32">
-        <v>407.7355310539168</v>
+        <v>403.1581461299925</v>
       </c>
       <c r="D32">
-        <v>515.1255310539167</v>
+        <v>515.1511461299924</v>
       </c>
       <c r="E32">
-        <v>-49.31000000000003</v>
+        <v>-44.70700000000002</v>
       </c>
       <c r="F32">
-        <v>138.09</v>
+        <v>142.693</v>
       </c>
       <c r="G32">
         <v>30.7</v>
@@ -3911,28 +3911,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M32">
-        <v>7.636376999999999</v>
+        <v>7.8909229</v>
       </c>
       <c r="N32">
-        <v>35.49695633333334</v>
+        <v>35.24241043333333</v>
       </c>
       <c r="O32">
-        <v>1.952332598333334</v>
+        <v>1.938332573833333</v>
       </c>
       <c r="P32">
-        <v>33.544623735</v>
+        <v>33.3040778595</v>
       </c>
       <c r="Q32">
-        <v>44.944623735</v>
+        <v>44.7040778595</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2271566669334139</v>
+        <v>0.2296821349860221</v>
       </c>
       <c r="T32">
-        <v>1.394164850576336</v>
+        <v>1.413579183943483</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.648402813707776</v>
+        <v>5.466196271330104</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1746808081403553</v>
+        <v>0.1746743994273208</v>
       </c>
       <c r="C33">
-        <v>403.1581461299925</v>
+        <v>398.5807637536603</v>
       </c>
       <c r="D33">
-        <v>515.1511461299924</v>
+        <v>515.1767637536602</v>
       </c>
       <c r="E33">
-        <v>-44.70700000000002</v>
+        <v>-40.10400000000001</v>
       </c>
       <c r="F33">
-        <v>142.693</v>
+        <v>147.296</v>
       </c>
       <c r="G33">
         <v>30.7</v>
@@ -3993,28 +3993,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M33">
-        <v>7.8909229</v>
+        <v>8.1454688</v>
       </c>
       <c r="N33">
-        <v>35.24241043333333</v>
+        <v>34.98786453333334</v>
       </c>
       <c r="O33">
-        <v>1.938332573833333</v>
+        <v>1.924332549333333</v>
       </c>
       <c r="P33">
-        <v>33.3040778595</v>
+        <v>33.063531984</v>
       </c>
       <c r="Q33">
-        <v>44.7040778595</v>
+        <v>44.463531984</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2296821349860221</v>
+        <v>0.2322818815107659</v>
       </c>
       <c r="T33">
-        <v>1.413579183943483</v>
+        <v>1.433564527115546</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.466196271330104</v>
+        <v>5.295377637851039</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1746743994273208</v>
+        <v>0.1746679907142864</v>
       </c>
       <c r="C34">
-        <v>398.5807637536603</v>
+        <v>394.0033839252993</v>
       </c>
       <c r="D34">
-        <v>515.1767637536602</v>
+        <v>515.2023839252993</v>
       </c>
       <c r="E34">
-        <v>-40.10400000000001</v>
+        <v>-35.501</v>
       </c>
       <c r="F34">
-        <v>147.296</v>
+        <v>151.899</v>
       </c>
       <c r="G34">
         <v>30.7</v>
@@ -4075,28 +4075,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M34">
-        <v>8.1454688</v>
+        <v>8.4000147</v>
       </c>
       <c r="N34">
-        <v>34.98786453333334</v>
+        <v>34.73331863333333</v>
       </c>
       <c r="O34">
-        <v>1.924332549333333</v>
+        <v>1.910332524833333</v>
       </c>
       <c r="P34">
-        <v>33.063531984</v>
+        <v>32.8229861085</v>
       </c>
       <c r="Q34">
-        <v>44.463531984</v>
+        <v>44.2229861085</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2322818815107659</v>
+        <v>0.2349592324093827</v>
       </c>
       <c r="T34">
-        <v>1.433564527115546</v>
+        <v>1.45414644769573</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.295377637851039</v>
+        <v>5.134911648825249</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1746679907142864</v>
+        <v>0.174661582001252</v>
       </c>
       <c r="C35">
-        <v>394.0033839252993</v>
+        <v>389.4260066452906</v>
       </c>
       <c r="D35">
-        <v>515.2023839252993</v>
+        <v>515.2280066452905</v>
       </c>
       <c r="E35">
-        <v>-35.501</v>
+        <v>-30.898</v>
       </c>
       <c r="F35">
-        <v>151.899</v>
+        <v>156.502</v>
       </c>
       <c r="G35">
         <v>30.7</v>
@@ -4157,28 +4157,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M35">
-        <v>8.4000147</v>
+        <v>8.654560600000002</v>
       </c>
       <c r="N35">
-        <v>34.73331863333333</v>
+        <v>34.47877273333333</v>
       </c>
       <c r="O35">
-        <v>1.910332524833333</v>
+        <v>1.896332500333333</v>
       </c>
       <c r="P35">
-        <v>32.8229861085</v>
+        <v>32.582440233</v>
       </c>
       <c r="Q35">
-        <v>44.2229861085</v>
+        <v>43.982440233</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2349592324093827</v>
+        <v>0.2377177151534121</v>
       </c>
       <c r="T35">
-        <v>1.45414644769573</v>
+        <v>1.47535206283895</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.134911648825249</v>
+        <v>4.983884835624506</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.174661582001252</v>
+        <v>0.1746551732882175</v>
       </c>
       <c r="C36">
-        <v>389.4260066452906</v>
+        <v>384.8486319140138</v>
       </c>
       <c r="D36">
-        <v>515.2280066452905</v>
+        <v>515.2536319140138</v>
       </c>
       <c r="E36">
-        <v>-30.898</v>
+        <v>-26.29500000000002</v>
       </c>
       <c r="F36">
-        <v>156.502</v>
+        <v>161.105</v>
       </c>
       <c r="G36">
         <v>30.7</v>
@@ -4239,28 +4239,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M36">
-        <v>8.654560600000002</v>
+        <v>8.9091065</v>
       </c>
       <c r="N36">
-        <v>34.47877273333333</v>
+        <v>34.22422683333333</v>
       </c>
       <c r="O36">
-        <v>1.896332500333333</v>
+        <v>1.882332475833333</v>
       </c>
       <c r="P36">
-        <v>32.582440233</v>
+        <v>32.3418943575</v>
       </c>
       <c r="Q36">
-        <v>43.982440233</v>
+        <v>43.7418943575</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2377177151534121</v>
+        <v>0.2405610742895654</v>
       </c>
       <c r="T36">
-        <v>1.47535206283895</v>
+        <v>1.497210158448116</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.983884835624506</v>
+        <v>4.841488126035236</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1746551732882175</v>
+        <v>0.1746487645751831</v>
       </c>
       <c r="C37">
-        <v>384.8486319140138</v>
+        <v>380.2712597318495</v>
       </c>
       <c r="D37">
-        <v>515.2536319140138</v>
+        <v>515.2792597318494</v>
       </c>
       <c r="E37">
-        <v>-26.29500000000002</v>
+        <v>-21.69200000000001</v>
       </c>
       <c r="F37">
-        <v>161.105</v>
+        <v>165.708</v>
       </c>
       <c r="G37">
         <v>30.7</v>
@@ -4321,28 +4321,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M37">
-        <v>8.9091065</v>
+        <v>9.1636524</v>
       </c>
       <c r="N37">
-        <v>34.22422683333333</v>
+        <v>33.96968093333334</v>
       </c>
       <c r="O37">
-        <v>1.882332475833333</v>
+        <v>1.868332451333333</v>
       </c>
       <c r="P37">
-        <v>32.3418943575</v>
+        <v>32.10134848200001</v>
       </c>
       <c r="Q37">
-        <v>43.7418943575</v>
+        <v>43.501348482</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2405610742895654</v>
+        <v>0.2434932883987236</v>
       </c>
       <c r="T37">
-        <v>1.497210158448116</v>
+        <v>1.519751319545068</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.841488126035236</v>
+        <v>4.707002344756479</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1746487645751831</v>
+        <v>0.1746423558621487</v>
       </c>
       <c r="C38">
-        <v>380.2712597318495</v>
+        <v>375.6938900991778</v>
       </c>
       <c r="D38">
-        <v>515.2792597318494</v>
+        <v>515.3048900991778</v>
       </c>
       <c r="E38">
-        <v>-21.69200000000004</v>
+        <v>-17.08900000000003</v>
       </c>
       <c r="F38">
-        <v>165.708</v>
+        <v>170.311</v>
       </c>
       <c r="G38">
         <v>30.7</v>
@@ -4403,28 +4403,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M38">
-        <v>9.163652399999998</v>
+        <v>9.418198299999998</v>
       </c>
       <c r="N38">
-        <v>33.96968093333334</v>
+        <v>33.71513503333333</v>
       </c>
       <c r="O38">
-        <v>1.868332451333333</v>
+        <v>1.854332426833333</v>
       </c>
       <c r="P38">
-        <v>32.10134848200001</v>
+        <v>31.8608026065</v>
       </c>
       <c r="Q38">
-        <v>43.501348482</v>
+        <v>43.2608026065</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2434932883987236</v>
+        <v>0.2465185886700772</v>
       </c>
       <c r="T38">
-        <v>1.519751319545067</v>
+        <v>1.543008073057795</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.707002344756479</v>
+        <v>4.579786065168467</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1746423558621487</v>
+        <v>0.1755336971491142</v>
       </c>
       <c r="C39">
-        <v>375.6938900991778</v>
+        <v>367.5504643346002</v>
       </c>
       <c r="D39">
-        <v>515.3048900991778</v>
+        <v>511.7644643346002</v>
       </c>
       <c r="E39">
-        <v>-17.08900000000003</v>
+        <v>-12.48600000000002</v>
       </c>
       <c r="F39">
-        <v>170.311</v>
+        <v>174.914</v>
       </c>
       <c r="G39">
         <v>30.7</v>
@@ -4485,45 +4485,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M39">
-        <v>9.418198299999998</v>
+        <v>10.1100292</v>
       </c>
       <c r="N39">
-        <v>33.71513503333333</v>
+        <v>33.02330413333333</v>
       </c>
       <c r="O39">
-        <v>1.854332426833333</v>
+        <v>1.816281727333333</v>
       </c>
       <c r="P39">
-        <v>31.8608026065</v>
+        <v>31.207022406</v>
       </c>
       <c r="Q39">
-        <v>43.2608026065</v>
+        <v>42.607022406</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2465185886700772</v>
+        <v>0.2496414792727649</v>
       </c>
       <c r="T39">
-        <v>1.543008073057795</v>
+        <v>1.567015044425773</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.055</v>
       </c>
       <c r="W39">
-        <v>0.0522585</v>
+        <v>0.054621</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.579786065168467</v>
+        <v>4.266390579102713</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1755336971491142</v>
+        <v>0.1755509134360798</v>
       </c>
       <c r="C40">
-        <v>367.5504643346002</v>
+        <v>362.8795597345982</v>
       </c>
       <c r="D40">
-        <v>511.7644643346002</v>
+        <v>511.6965597345982</v>
       </c>
       <c r="E40">
-        <v>-12.48600000000002</v>
+        <v>-7.88300000000001</v>
       </c>
       <c r="F40">
-        <v>174.914</v>
+        <v>179.517</v>
       </c>
       <c r="G40">
         <v>30.7</v>
@@ -4567,28 +4567,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M40">
-        <v>10.1100292</v>
+        <v>10.3760826</v>
       </c>
       <c r="N40">
-        <v>33.02330413333333</v>
+        <v>32.75725073333334</v>
       </c>
       <c r="O40">
-        <v>1.816281727333333</v>
+        <v>1.801648790333334</v>
       </c>
       <c r="P40">
-        <v>31.207022406</v>
+        <v>30.955601943</v>
       </c>
       <c r="Q40">
-        <v>42.607022406</v>
+        <v>42.355601943</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2496414792727649</v>
+        <v>0.2528667597312784</v>
       </c>
       <c r="T40">
-        <v>1.567015044425773</v>
+        <v>1.591809129609094</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.266390579102713</v>
+        <v>4.15699594886931</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1755509134360798</v>
+        <v>0.1755681297230454</v>
       </c>
       <c r="C41">
-        <v>362.8795597345982</v>
+        <v>358.2086731523497</v>
       </c>
       <c r="D41">
-        <v>511.6965597345982</v>
+        <v>511.6286731523496</v>
       </c>
       <c r="E41">
-        <v>-7.88300000000001</v>
+        <v>-3.280000000000001</v>
       </c>
       <c r="F41">
-        <v>179.517</v>
+        <v>184.12</v>
       </c>
       <c r="G41">
         <v>30.7</v>
@@ -4649,28 +4649,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M41">
-        <v>10.3760826</v>
+        <v>10.642136</v>
       </c>
       <c r="N41">
-        <v>32.75725073333334</v>
+        <v>32.49119733333333</v>
       </c>
       <c r="O41">
-        <v>1.801648790333334</v>
+        <v>1.787015853333333</v>
       </c>
       <c r="P41">
-        <v>30.955601943</v>
+        <v>30.70418148</v>
       </c>
       <c r="Q41">
-        <v>42.355601943</v>
+        <v>42.10418148</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2528667597312784</v>
+        <v>0.2561995495384089</v>
       </c>
       <c r="T41">
-        <v>1.591809129609094</v>
+        <v>1.617429684298525</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.15699594886931</v>
+        <v>4.053071050147576</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1755681297230454</v>
+        <v>0.1769414210100109</v>
       </c>
       <c r="C42">
-        <v>358.2086731523497</v>
+        <v>348.2479822443929</v>
       </c>
       <c r="D42">
-        <v>511.6286731523496</v>
+        <v>506.2709822443929</v>
       </c>
       <c r="E42">
-        <v>-3.280000000000001</v>
+        <v>1.322999999999979</v>
       </c>
       <c r="F42">
-        <v>184.12</v>
+        <v>188.723</v>
       </c>
       <c r="G42">
         <v>30.7</v>
@@ -4731,45 +4731,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M42">
-        <v>10.642136</v>
+        <v>11.5687199</v>
       </c>
       <c r="N42">
-        <v>32.49119733333333</v>
+        <v>31.56461343333334</v>
       </c>
       <c r="O42">
-        <v>1.787015853333333</v>
+        <v>1.736053738833333</v>
       </c>
       <c r="P42">
-        <v>30.70418148</v>
+        <v>29.8285596945</v>
       </c>
       <c r="Q42">
-        <v>42.10418148</v>
+        <v>41.2285596945</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2561995495384089</v>
+        <v>0.2596453152712049</v>
       </c>
       <c r="T42">
-        <v>1.617429684298525</v>
+        <v>1.643918732367259</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.055</v>
       </c>
       <c r="W42">
-        <v>0.054621</v>
+        <v>0.05792849999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.053071050147576</v>
+        <v>3.728444780941869</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1769414210100109</v>
+        <v>0.1769917122969765</v>
       </c>
       <c r="C43">
-        <v>348.2479822443929</v>
+        <v>343.4509073382526</v>
       </c>
       <c r="D43">
-        <v>506.2709822443929</v>
+        <v>506.0769073382526</v>
       </c>
       <c r="E43">
-        <v>1.322999999999979</v>
+        <v>5.925999999999988</v>
       </c>
       <c r="F43">
-        <v>188.723</v>
+        <v>193.326</v>
       </c>
       <c r="G43">
         <v>30.7</v>
@@ -4813,28 +4813,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M43">
-        <v>11.5687199</v>
+        <v>11.8508838</v>
       </c>
       <c r="N43">
-        <v>31.56461343333334</v>
+        <v>31.28244953333333</v>
       </c>
       <c r="O43">
-        <v>1.736053738833333</v>
+        <v>1.720534724333333</v>
       </c>
       <c r="P43">
-        <v>29.8285596945</v>
+        <v>29.561914809</v>
       </c>
       <c r="Q43">
-        <v>41.2285596945</v>
+        <v>40.961914809</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2596453152712049</v>
+        <v>0.2632099005120285</v>
       </c>
       <c r="T43">
-        <v>1.643918732367259</v>
+        <v>1.67132119588664</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.728444780941869</v>
+        <v>3.639672286157538</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1769917122969765</v>
+        <v>0.1770420035839421</v>
       </c>
       <c r="C44">
-        <v>343.4509073382528</v>
+        <v>338.6539811692019</v>
       </c>
       <c r="D44">
-        <v>506.0769073382527</v>
+        <v>505.8829811692018</v>
       </c>
       <c r="E44">
-        <v>5.925999999999959</v>
+        <v>10.52899999999997</v>
       </c>
       <c r="F44">
-        <v>193.326</v>
+        <v>197.929</v>
       </c>
       <c r="G44">
         <v>30.7</v>
@@ -4895,28 +4895,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M44">
-        <v>11.8508838</v>
+        <v>12.1330477</v>
       </c>
       <c r="N44">
-        <v>31.28244953333333</v>
+        <v>31.00028563333333</v>
       </c>
       <c r="O44">
-        <v>1.720534724333333</v>
+        <v>1.705015709833333</v>
       </c>
       <c r="P44">
-        <v>29.561914809</v>
+        <v>29.2952699235</v>
       </c>
       <c r="Q44">
-        <v>40.961914809</v>
+        <v>40.6952699235</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2632099005120284</v>
+        <v>0.2668995589191966</v>
       </c>
       <c r="T44">
-        <v>1.67132119588664</v>
+        <v>1.699685149354068</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.639672286157539</v>
+        <v>3.555028744618991</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1770420035839421</v>
+        <v>0.1782565348709076</v>
       </c>
       <c r="C45">
-        <v>338.6539811692019</v>
+        <v>329.4123975857477</v>
       </c>
       <c r="D45">
-        <v>505.8829811692018</v>
+        <v>501.2443975857477</v>
       </c>
       <c r="E45">
-        <v>10.52899999999997</v>
+        <v>15.13199999999998</v>
       </c>
       <c r="F45">
-        <v>197.929</v>
+        <v>202.532</v>
       </c>
       <c r="G45">
         <v>30.7</v>
@@ -4977,45 +4977,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M45">
-        <v>12.1330477</v>
+        <v>12.9823012</v>
       </c>
       <c r="N45">
-        <v>31.00028563333333</v>
+        <v>30.15103213333333</v>
       </c>
       <c r="O45">
-        <v>1.705015709833333</v>
+        <v>1.658306767333333</v>
       </c>
       <c r="P45">
-        <v>29.2952699235</v>
+        <v>28.492725366</v>
       </c>
       <c r="Q45">
-        <v>40.6952699235</v>
+        <v>39.892725366</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2668995589191966</v>
+        <v>0.2707209908409065</v>
       </c>
       <c r="T45">
-        <v>1.699685149354068</v>
+        <v>1.72906210115962</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.055</v>
       </c>
       <c r="W45">
-        <v>0.05792849999999999</v>
+        <v>0.0605745</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.555028744618991</v>
+        <v>3.322472084789816</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1782565348709076</v>
+        <v>0.1783332861578732</v>
       </c>
       <c r="C46">
-        <v>329.4123975857477</v>
+        <v>324.5191221861537</v>
       </c>
       <c r="D46">
-        <v>501.2443975857477</v>
+        <v>500.9541221861537</v>
       </c>
       <c r="E46">
-        <v>15.13199999999998</v>
+        <v>19.73499999999999</v>
       </c>
       <c r="F46">
-        <v>202.532</v>
+        <v>207.135</v>
       </c>
       <c r="G46">
         <v>30.7</v>
@@ -5059,28 +5059,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M46">
-        <v>12.9823012</v>
+        <v>13.2773535</v>
       </c>
       <c r="N46">
-        <v>30.15103213333333</v>
+        <v>29.85597983333333</v>
       </c>
       <c r="O46">
-        <v>1.658306767333333</v>
+        <v>1.642078890833333</v>
       </c>
       <c r="P46">
-        <v>28.492725366</v>
+        <v>28.2139009425</v>
       </c>
       <c r="Q46">
-        <v>39.892725366</v>
+        <v>39.6139009425</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2707209908409065</v>
+        <v>0.2746813839234058</v>
       </c>
       <c r="T46">
-        <v>1.72906210115962</v>
+        <v>1.7595073057581</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.322472084789816</v>
+        <v>3.248639371794487</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1783332861578732</v>
+        <v>0.1784100374448387</v>
       </c>
       <c r="C47">
-        <v>324.5191221861537</v>
+        <v>319.6261827944656</v>
       </c>
       <c r="D47">
-        <v>500.9541221861537</v>
+        <v>500.6641827944656</v>
       </c>
       <c r="E47">
-        <v>19.73499999999999</v>
+        <v>24.33799999999999</v>
       </c>
       <c r="F47">
-        <v>207.135</v>
+        <v>211.738</v>
       </c>
       <c r="G47">
         <v>30.7</v>
@@ -5141,28 +5141,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M47">
-        <v>13.2773535</v>
+        <v>13.5724058</v>
       </c>
       <c r="N47">
-        <v>29.85597983333333</v>
+        <v>29.56092753333333</v>
       </c>
       <c r="O47">
-        <v>1.642078890833333</v>
+        <v>1.625851014333333</v>
       </c>
       <c r="P47">
-        <v>28.2139009425</v>
+        <v>27.935076519</v>
       </c>
       <c r="Q47">
-        <v>39.6139009425</v>
+        <v>39.335076519</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2746813839234058</v>
+        <v>0.2787884582311829</v>
       </c>
       <c r="T47">
-        <v>1.7595073057581</v>
+        <v>1.791080110526894</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.248639371794487</v>
+        <v>3.178016776755476</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1784100374448387</v>
+        <v>0.1784867887318043</v>
       </c>
       <c r="C48">
-        <v>319.6261827944656</v>
+        <v>314.7335788276025</v>
       </c>
       <c r="D48">
-        <v>500.6641827944656</v>
+        <v>500.3745788276025</v>
       </c>
       <c r="E48">
-        <v>24.33799999999999</v>
+        <v>28.94099999999997</v>
       </c>
       <c r="F48">
-        <v>211.738</v>
+        <v>216.341</v>
       </c>
       <c r="G48">
         <v>30.7</v>
@@ -5223,28 +5223,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M48">
-        <v>13.5724058</v>
+        <v>13.8674581</v>
       </c>
       <c r="N48">
-        <v>29.56092753333333</v>
+        <v>29.26587523333333</v>
       </c>
       <c r="O48">
-        <v>1.625851014333333</v>
+        <v>1.609623137833333</v>
       </c>
       <c r="P48">
-        <v>27.935076519</v>
+        <v>27.6562520955</v>
       </c>
       <c r="Q48">
-        <v>39.335076519</v>
+        <v>39.0562520955</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2787884582311829</v>
+        <v>0.2830505164751025</v>
       </c>
       <c r="T48">
-        <v>1.791080110526894</v>
+        <v>1.823844341890738</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.178016776755476</v>
+        <v>3.110399398526636</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1784867887318043</v>
+        <v>0.1785635400187699</v>
       </c>
       <c r="C49">
-        <v>314.7335788276025</v>
+        <v>309.8413097038324</v>
       </c>
       <c r="D49">
-        <v>500.3745788276025</v>
+        <v>500.0853097038324</v>
       </c>
       <c r="E49">
-        <v>28.94099999999997</v>
+        <v>33.54399999999998</v>
       </c>
       <c r="F49">
-        <v>216.341</v>
+        <v>220.944</v>
       </c>
       <c r="G49">
         <v>30.7</v>
@@ -5305,28 +5305,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M49">
-        <v>13.8674581</v>
+        <v>14.1625104</v>
       </c>
       <c r="N49">
-        <v>29.26587523333333</v>
+        <v>28.97082293333333</v>
       </c>
       <c r="O49">
-        <v>1.609623137833333</v>
+        <v>1.593395261333333</v>
       </c>
       <c r="P49">
-        <v>27.6562520955</v>
+        <v>27.377427672</v>
       </c>
       <c r="Q49">
-        <v>39.0562520955</v>
+        <v>38.77742767199999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2830505164751025</v>
+        <v>0.2874765000360959</v>
       </c>
       <c r="T49">
-        <v>1.823844341890738</v>
+        <v>1.857868735999344</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.110399398526636</v>
+        <v>3.045599411057331</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1785635400187699</v>
+        <v>0.1822520813057354</v>
       </c>
       <c r="C50">
-        <v>309.8413097038324</v>
+        <v>291.7201185982343</v>
       </c>
       <c r="D50">
-        <v>500.0853097038324</v>
+        <v>486.5671185982342</v>
       </c>
       <c r="E50">
-        <v>33.54399999999995</v>
+        <v>38.14699999999996</v>
       </c>
       <c r="F50">
-        <v>220.944</v>
+        <v>225.547</v>
       </c>
       <c r="G50">
         <v>30.7</v>
@@ -5387,45 +5387,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M50">
-        <v>14.1625104</v>
+        <v>16.2168293</v>
       </c>
       <c r="N50">
-        <v>28.97082293333333</v>
+        <v>26.91650403333333</v>
       </c>
       <c r="O50">
-        <v>1.593395261333333</v>
+        <v>1.480407721833333</v>
       </c>
       <c r="P50">
-        <v>27.377427672</v>
+        <v>25.4360963115</v>
       </c>
       <c r="Q50">
-        <v>38.777427672</v>
+        <v>36.8360963115</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2874765000360959</v>
+        <v>0.2920760515798734</v>
       </c>
       <c r="T50">
-        <v>1.857868735999344</v>
+        <v>1.893227420072994</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.055</v>
       </c>
       <c r="W50">
-        <v>0.0605745</v>
+        <v>0.06794550000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.045599411057332</v>
+        <v>2.659788330714767</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1822520813057354</v>
+        <v>0.182402542592701</v>
       </c>
       <c r="C51">
-        <v>291.7201185982343</v>
+        <v>286.5811877621758</v>
       </c>
       <c r="D51">
-        <v>486.5671185982342</v>
+        <v>486.0311877621758</v>
       </c>
       <c r="E51">
-        <v>38.14699999999996</v>
+        <v>42.74999999999997</v>
       </c>
       <c r="F51">
-        <v>225.547</v>
+        <v>230.15</v>
       </c>
       <c r="G51">
         <v>30.7</v>
@@ -5469,28 +5469,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M51">
-        <v>16.2168293</v>
+        <v>16.547785</v>
       </c>
       <c r="N51">
-        <v>26.91650403333333</v>
+        <v>26.58554833333333</v>
       </c>
       <c r="O51">
-        <v>1.480407721833333</v>
+        <v>1.462205158333333</v>
       </c>
       <c r="P51">
-        <v>25.4360963115</v>
+        <v>25.123343175</v>
       </c>
       <c r="Q51">
-        <v>36.8360963115</v>
+        <v>36.523343175</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2920760515798734</v>
+        <v>0.2968595851854021</v>
       </c>
       <c r="T51">
-        <v>1.893227420072994</v>
+        <v>1.93000045150959</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.659788330714767</v>
+        <v>2.606592564100472</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.182402542592701</v>
+        <v>0.1825530038796666</v>
       </c>
       <c r="C52">
-        <v>286.5811877621758</v>
+        <v>281.4434362324729</v>
       </c>
       <c r="D52">
-        <v>486.0311877621758</v>
+        <v>485.4964362324729</v>
       </c>
       <c r="E52">
-        <v>42.74999999999997</v>
+        <v>47.35299999999998</v>
       </c>
       <c r="F52">
-        <v>230.15</v>
+        <v>234.753</v>
       </c>
       <c r="G52">
         <v>30.7</v>
@@ -5551,28 +5551,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M52">
-        <v>16.547785</v>
+        <v>16.8787407</v>
       </c>
       <c r="N52">
-        <v>26.58554833333333</v>
+        <v>26.25459263333333</v>
       </c>
       <c r="O52">
-        <v>1.462205158333333</v>
+        <v>1.444002594833333</v>
       </c>
       <c r="P52">
-        <v>25.123343175</v>
+        <v>24.8105900385</v>
       </c>
       <c r="Q52">
-        <v>36.523343175</v>
+        <v>36.2105900385</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2968595851854021</v>
+        <v>0.3018383650605441</v>
       </c>
       <c r="T52">
-        <v>1.93000045150959</v>
+        <v>1.968274423004822</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.606592564100472</v>
+        <v>2.555482905980855</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1825530038796666</v>
+        <v>0.1827034651666322</v>
       </c>
       <c r="C53">
-        <v>281.4434362324729</v>
+        <v>276.3068601208397</v>
       </c>
       <c r="D53">
-        <v>485.4964362324729</v>
+        <v>484.9628601208397</v>
       </c>
       <c r="E53">
-        <v>47.35299999999998</v>
+        <v>51.95599999999999</v>
       </c>
       <c r="F53">
-        <v>234.753</v>
+        <v>239.356</v>
       </c>
       <c r="G53">
         <v>30.7</v>
@@ -5633,28 +5633,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M53">
-        <v>16.8787407</v>
+        <v>17.2096964</v>
       </c>
       <c r="N53">
-        <v>26.25459263333333</v>
+        <v>25.92363693333333</v>
       </c>
       <c r="O53">
-        <v>1.444002594833333</v>
+        <v>1.425800031333333</v>
       </c>
       <c r="P53">
-        <v>24.8105900385</v>
+        <v>24.497836902</v>
       </c>
       <c r="Q53">
-        <v>36.2105900385</v>
+        <v>35.89783690199999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3018383650605441</v>
+        <v>0.3070245940971504</v>
       </c>
       <c r="T53">
-        <v>1.968274423004822</v>
+        <v>2.008143143312356</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.555482905980855</v>
+        <v>2.506339003942761</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1827034651666322</v>
+        <v>0.1848072414535977</v>
       </c>
       <c r="C54">
-        <v>276.3068601208397</v>
+        <v>264.3642902213695</v>
       </c>
       <c r="D54">
-        <v>484.9628601208397</v>
+        <v>477.6232902213695</v>
       </c>
       <c r="E54">
-        <v>51.95599999999999</v>
+        <v>56.55899999999997</v>
       </c>
       <c r="F54">
-        <v>239.356</v>
+        <v>243.959</v>
       </c>
       <c r="G54">
         <v>30.7</v>
@@ -5715,45 +5715,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M54">
-        <v>17.2096964</v>
+        <v>18.4920922</v>
       </c>
       <c r="N54">
-        <v>25.92363693333333</v>
+        <v>24.64124113333333</v>
       </c>
       <c r="O54">
-        <v>1.425800031333333</v>
+        <v>1.355268262333333</v>
       </c>
       <c r="P54">
-        <v>24.497836902</v>
+        <v>23.285972871</v>
       </c>
       <c r="Q54">
-        <v>35.89783690199999</v>
+        <v>34.685972871</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3070245940971504</v>
+        <v>0.312431513731059</v>
       </c>
       <c r="T54">
-        <v>2.008143143312356</v>
+        <v>2.049708404909572</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.055</v>
       </c>
       <c r="W54">
-        <v>0.06794550000000001</v>
+        <v>0.071631</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.506339003942761</v>
+        <v>2.332528567715736</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1848072414535977</v>
+        <v>0.1849945577405633</v>
       </c>
       <c r="C55">
-        <v>264.3642902213695</v>
+        <v>259.1185451116124</v>
       </c>
       <c r="D55">
-        <v>477.6232902213695</v>
+        <v>476.9805451116124</v>
       </c>
       <c r="E55">
-        <v>56.55899999999997</v>
+        <v>61.16199999999998</v>
       </c>
       <c r="F55">
-        <v>243.959</v>
+        <v>248.562</v>
       </c>
       <c r="G55">
         <v>30.7</v>
@@ -5797,28 +5797,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M55">
-        <v>18.4920922</v>
+        <v>18.8409996</v>
       </c>
       <c r="N55">
-        <v>24.64124113333333</v>
+        <v>24.29233373333333</v>
       </c>
       <c r="O55">
-        <v>1.355268262333333</v>
+        <v>1.336078355333333</v>
       </c>
       <c r="P55">
-        <v>23.285972871</v>
+        <v>22.956255378</v>
       </c>
       <c r="Q55">
-        <v>34.685972871</v>
+        <v>34.356255378</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.312431513731059</v>
+        <v>0.3180735168273116</v>
       </c>
       <c r="T55">
-        <v>2.049708404909572</v>
+        <v>2.093080851793624</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.332528567715736</v>
+        <v>2.289333594239519</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1849945577405633</v>
+        <v>0.1851818740275289</v>
       </c>
       <c r="C56">
-        <v>259.1185451116124</v>
+        <v>253.8745275812591</v>
       </c>
       <c r="D56">
-        <v>476.9805451116124</v>
+        <v>476.3395275812591</v>
       </c>
       <c r="E56">
-        <v>61.16199999999998</v>
+        <v>65.76499999999999</v>
       </c>
       <c r="F56">
-        <v>248.562</v>
+        <v>253.165</v>
       </c>
       <c r="G56">
         <v>30.7</v>
@@ -5879,28 +5879,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M56">
-        <v>18.8409996</v>
+        <v>19.189907</v>
       </c>
       <c r="N56">
-        <v>24.29233373333333</v>
+        <v>23.94342633333333</v>
       </c>
       <c r="O56">
-        <v>1.336078355333333</v>
+        <v>1.316888448333333</v>
       </c>
       <c r="P56">
-        <v>22.956255378</v>
+        <v>22.626537885</v>
       </c>
       <c r="Q56">
-        <v>34.356255378</v>
+        <v>34.026537885</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3180735168273116</v>
+        <v>0.3239662756167309</v>
       </c>
       <c r="T56">
-        <v>2.093080851793624</v>
+        <v>2.138380962983633</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.289333594239519</v>
+        <v>2.247709347071527</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1851818740275289</v>
+        <v>0.1853691903144944</v>
       </c>
       <c r="C57">
-        <v>253.8745275812591</v>
+        <v>248.6322306745393</v>
       </c>
       <c r="D57">
-        <v>476.3395275812591</v>
+        <v>475.7002306745393</v>
       </c>
       <c r="E57">
-        <v>65.76499999999999</v>
+        <v>70.36799999999997</v>
       </c>
       <c r="F57">
-        <v>253.165</v>
+        <v>257.768</v>
       </c>
       <c r="G57">
         <v>30.7</v>
@@ -5961,28 +5961,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M57">
-        <v>19.189907</v>
+        <v>19.5388144</v>
       </c>
       <c r="N57">
-        <v>23.94342633333333</v>
+        <v>23.59451893333333</v>
       </c>
       <c r="O57">
-        <v>1.316888448333333</v>
+        <v>1.297698541333333</v>
       </c>
       <c r="P57">
-        <v>22.626537885</v>
+        <v>22.296820392</v>
       </c>
       <c r="Q57">
-        <v>34.026537885</v>
+        <v>33.696820392</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3239662756167309</v>
+        <v>0.3301268870783965</v>
       </c>
       <c r="T57">
-        <v>2.138380962983633</v>
+        <v>2.185740170136825</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.247709347071527</v>
+        <v>2.207571680159536</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1853691903144944</v>
+        <v>0.18555650660146</v>
       </c>
       <c r="C58">
-        <v>248.6322306745393</v>
+        <v>243.3916474729735</v>
       </c>
       <c r="D58">
-        <v>475.7002306745393</v>
+        <v>475.0626474729735</v>
       </c>
       <c r="E58">
-        <v>70.36799999999997</v>
+        <v>74.97099999999998</v>
       </c>
       <c r="F58">
-        <v>257.768</v>
+        <v>262.371</v>
       </c>
       <c r="G58">
         <v>30.7</v>
@@ -6043,28 +6043,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M58">
-        <v>19.5388144</v>
+        <v>19.8877218</v>
       </c>
       <c r="N58">
-        <v>23.59451893333333</v>
+        <v>23.24561153333333</v>
       </c>
       <c r="O58">
-        <v>1.297698541333333</v>
+        <v>1.278508634333333</v>
       </c>
       <c r="P58">
-        <v>22.296820392</v>
+        <v>21.967102899</v>
       </c>
       <c r="Q58">
-        <v>33.696820392</v>
+        <v>33.367102899</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3301268870783965</v>
+        <v>0.3365740386080465</v>
       </c>
       <c r="T58">
-        <v>2.185740170136825</v>
+        <v>2.235302131111095</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.207571680159536</v>
+        <v>2.168842352437439</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.18555650660146</v>
+        <v>0.1857438228884256</v>
       </c>
       <c r="C59">
-        <v>243.3916474729735</v>
+        <v>238.1527710951242</v>
       </c>
       <c r="D59">
-        <v>475.0626474729735</v>
+        <v>474.4267710951242</v>
       </c>
       <c r="E59">
-        <v>74.97099999999998</v>
+        <v>79.57399999999998</v>
       </c>
       <c r="F59">
-        <v>262.371</v>
+        <v>266.974</v>
       </c>
       <c r="G59">
         <v>30.7</v>
@@ -6125,28 +6125,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M59">
-        <v>19.8877218</v>
+        <v>20.2366292</v>
       </c>
       <c r="N59">
-        <v>23.24561153333333</v>
+        <v>22.89670413333333</v>
       </c>
       <c r="O59">
-        <v>1.278508634333333</v>
+        <v>1.259318727333333</v>
       </c>
       <c r="P59">
-        <v>21.967102899</v>
+        <v>21.637385406</v>
       </c>
       <c r="Q59">
-        <v>33.367102899</v>
+        <v>33.037385406</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3365740386080465</v>
+        <v>0.3433281973533943</v>
       </c>
       <c r="T59">
-        <v>2.235302131111095</v>
+        <v>2.287224185465093</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.168842352437439</v>
+        <v>2.131448518774724</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1857438228884256</v>
+        <v>0.1859311391753911</v>
       </c>
       <c r="C60">
-        <v>238.1527710951243</v>
+        <v>232.9155946963484</v>
       </c>
       <c r="D60">
-        <v>474.4267710951242</v>
+        <v>473.7925946963483</v>
       </c>
       <c r="E60">
-        <v>79.57399999999993</v>
+        <v>84.17699999999994</v>
       </c>
       <c r="F60">
-        <v>266.9739999999999</v>
+        <v>271.5769999999999</v>
       </c>
       <c r="G60">
         <v>30.7</v>
@@ -6207,28 +6207,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M60">
-        <v>20.2366292</v>
+        <v>20.5855366</v>
       </c>
       <c r="N60">
-        <v>22.89670413333334</v>
+        <v>22.54779673333334</v>
       </c>
       <c r="O60">
-        <v>1.259318727333333</v>
+        <v>1.240128820333333</v>
       </c>
       <c r="P60">
-        <v>21.637385406</v>
+        <v>21.307667913</v>
       </c>
       <c r="Q60">
-        <v>33.03738540600001</v>
+        <v>32.707667913</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3433281973533942</v>
+        <v>0.3504118272570515</v>
       </c>
       <c r="T60">
-        <v>2.287224185465092</v>
+        <v>2.341679022958309</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.131448518774725</v>
+        <v>2.095322272693797</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1859311391753911</v>
+        <v>0.1861184554623567</v>
       </c>
       <c r="C61">
-        <v>232.9155946963484</v>
+        <v>227.6801114685514</v>
       </c>
       <c r="D61">
-        <v>473.7925946963483</v>
+        <v>473.1601114685514</v>
       </c>
       <c r="E61">
-        <v>84.17699999999994</v>
+        <v>88.77999999999994</v>
       </c>
       <c r="F61">
-        <v>271.5769999999999</v>
+        <v>276.1799999999999</v>
       </c>
       <c r="G61">
         <v>30.7</v>
@@ -6289,28 +6289,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M61">
-        <v>20.5855366</v>
+        <v>20.934444</v>
       </c>
       <c r="N61">
-        <v>22.54779673333334</v>
+        <v>22.19888933333333</v>
       </c>
       <c r="O61">
-        <v>1.240128820333333</v>
+        <v>1.220938913333333</v>
       </c>
       <c r="P61">
-        <v>21.307667913</v>
+        <v>20.97795042</v>
       </c>
       <c r="Q61">
-        <v>32.707667913</v>
+        <v>32.37795042</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3504118272570515</v>
+        <v>0.3578496386558918</v>
       </c>
       <c r="T61">
-        <v>2.341679022958309</v>
+        <v>2.398856602326187</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.095322272693797</v>
+        <v>2.060400234815567</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1861184554623567</v>
+        <v>0.1863057717493223</v>
       </c>
       <c r="C62">
-        <v>227.6801114685514</v>
+        <v>222.4463146399441</v>
       </c>
       <c r="D62">
-        <v>473.1601114685514</v>
+        <v>472.5293146399441</v>
       </c>
       <c r="E62">
-        <v>88.77999999999994</v>
+        <v>93.38299999999995</v>
       </c>
       <c r="F62">
-        <v>276.1799999999999</v>
+        <v>280.783</v>
       </c>
       <c r="G62">
         <v>30.7</v>
@@ -6371,28 +6371,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M62">
-        <v>20.934444</v>
+        <v>21.2833514</v>
       </c>
       <c r="N62">
-        <v>22.19888933333333</v>
+        <v>21.84998193333334</v>
       </c>
       <c r="O62">
-        <v>1.220938913333333</v>
+        <v>1.201749006333333</v>
       </c>
       <c r="P62">
-        <v>20.97795042</v>
+        <v>20.648232927</v>
       </c>
       <c r="Q62">
-        <v>32.37795042</v>
+        <v>32.048232927</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3578496386558918</v>
+        <v>0.3656688762803135</v>
       </c>
       <c r="T62">
-        <v>2.398856602326187</v>
+        <v>2.458966365251392</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.060400234815567</v>
+        <v>2.026623181785804</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1863057717493223</v>
+        <v>0.1948128680362878</v>
       </c>
       <c r="C63">
-        <v>222.4463146399441</v>
+        <v>190.8667693856314</v>
       </c>
       <c r="D63">
-        <v>472.5293146399441</v>
+        <v>445.5527693856314</v>
       </c>
       <c r="E63">
-        <v>93.38299999999995</v>
+        <v>97.98599999999996</v>
       </c>
       <c r="F63">
-        <v>280.783</v>
+        <v>285.386</v>
       </c>
       <c r="G63">
         <v>30.7</v>
@@ -6453,45 +6453,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M63">
-        <v>21.2833514</v>
+        <v>25.68473999999999</v>
       </c>
       <c r="N63">
-        <v>21.84998193333334</v>
+        <v>17.44859333333334</v>
       </c>
       <c r="O63">
-        <v>1.201749006333333</v>
+        <v>0.9596726333333336</v>
       </c>
       <c r="P63">
-        <v>20.648232927</v>
+        <v>16.4889207</v>
       </c>
       <c r="Q63">
-        <v>32.048232927</v>
+        <v>27.88892070000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3656688762803135</v>
+        <v>0.3738996527270733</v>
       </c>
       <c r="T63">
-        <v>2.458966365251392</v>
+        <v>2.522239799909502</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.055</v>
       </c>
       <c r="W63">
-        <v>0.071631</v>
+        <v>0.08504999999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.026623181785804</v>
+        <v>1.67933696558086</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1948128680362878</v>
+        <v>0.1951343743232534</v>
       </c>
       <c r="C64">
-        <v>190.8667693856314</v>
+        <v>185.3045259617273</v>
       </c>
       <c r="D64">
-        <v>445.5527693856314</v>
+        <v>444.5935259617273</v>
       </c>
       <c r="E64">
-        <v>97.98599999999996</v>
+        <v>102.589</v>
       </c>
       <c r="F64">
-        <v>285.386</v>
+        <v>289.989</v>
       </c>
       <c r="G64">
         <v>30.7</v>
@@ -6535,28 +6535,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M64">
-        <v>25.68473999999999</v>
+        <v>26.09901</v>
       </c>
       <c r="N64">
-        <v>17.44859333333334</v>
+        <v>17.03432333333334</v>
       </c>
       <c r="O64">
-        <v>0.9596726333333336</v>
+        <v>0.9368877833333336</v>
       </c>
       <c r="P64">
-        <v>16.4889207</v>
+        <v>16.09743555</v>
       </c>
       <c r="Q64">
-        <v>27.88892070000001</v>
+        <v>27.49743555000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3738996527270733</v>
+        <v>0.382575336008793</v>
       </c>
       <c r="T64">
-        <v>2.522239799909502</v>
+        <v>2.588933420224807</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.67933696558086</v>
+        <v>1.652680823270053</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1951343743232534</v>
+        <v>0.195455880610219</v>
       </c>
       <c r="C65">
-        <v>185.3045259617273</v>
+        <v>179.7464040302801</v>
       </c>
       <c r="D65">
-        <v>444.5935259617273</v>
+        <v>443.6384040302801</v>
       </c>
       <c r="E65">
-        <v>102.589</v>
+        <v>107.192</v>
       </c>
       <c r="F65">
-        <v>289.989</v>
+        <v>294.592</v>
       </c>
       <c r="G65">
         <v>30.7</v>
@@ -6617,28 +6617,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M65">
-        <v>26.09901</v>
+        <v>26.51328</v>
       </c>
       <c r="N65">
-        <v>17.03432333333334</v>
+        <v>16.62005333333333</v>
       </c>
       <c r="O65">
-        <v>0.9368877833333336</v>
+        <v>0.9141029333333334</v>
       </c>
       <c r="P65">
-        <v>16.09743555</v>
+        <v>15.7059504</v>
       </c>
       <c r="Q65">
-        <v>27.49743555000001</v>
+        <v>27.1059504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.382575336008793</v>
+        <v>0.3917330016950527</v>
       </c>
       <c r="T65">
-        <v>2.588933420224807</v>
+        <v>2.659332241668741</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.652680823270053</v>
+        <v>1.626857685406458</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.195455880610219</v>
+        <v>0.1957773868971845</v>
       </c>
       <c r="C66">
-        <v>179.7464040302801</v>
+        <v>174.1923770855789</v>
       </c>
       <c r="D66">
-        <v>443.6384040302801</v>
+        <v>442.6873770855789</v>
       </c>
       <c r="E66">
-        <v>107.192</v>
+        <v>111.795</v>
       </c>
       <c r="F66">
-        <v>294.592</v>
+        <v>299.195</v>
       </c>
       <c r="G66">
         <v>30.7</v>
@@ -6699,28 +6699,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M66">
-        <v>26.51328</v>
+        <v>26.92755</v>
       </c>
       <c r="N66">
-        <v>16.62005333333333</v>
+        <v>16.20578333333333</v>
       </c>
       <c r="O66">
-        <v>0.9141029333333334</v>
+        <v>0.8913180833333333</v>
       </c>
       <c r="P66">
-        <v>15.7059504</v>
+        <v>15.31446525</v>
       </c>
       <c r="Q66">
-        <v>27.1059504</v>
+        <v>26.71446525</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3917330016950527</v>
+        <v>0.4014139625633844</v>
       </c>
       <c r="T66">
-        <v>2.659332241668741</v>
+        <v>2.73375385290947</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.626857685406458</v>
+        <v>1.601829105630974</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1957773868971845</v>
+        <v>0.1960988931841501</v>
       </c>
       <c r="C67">
-        <v>174.1923770855789</v>
+        <v>168.6424188487079</v>
       </c>
       <c r="D67">
-        <v>442.6873770855789</v>
+        <v>441.7404188487079</v>
       </c>
       <c r="E67">
-        <v>111.795</v>
+        <v>116.398</v>
       </c>
       <c r="F67">
-        <v>299.195</v>
+        <v>303.798</v>
       </c>
       <c r="G67">
         <v>30.7</v>
@@ -6781,28 +6781,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M67">
-        <v>26.92755</v>
+        <v>27.34182</v>
       </c>
       <c r="N67">
-        <v>16.20578333333333</v>
+        <v>15.79151333333333</v>
       </c>
       <c r="O67">
-        <v>0.8913180833333333</v>
+        <v>0.8685332333333334</v>
       </c>
       <c r="P67">
-        <v>15.31446525</v>
+        <v>14.9229801</v>
       </c>
       <c r="Q67">
-        <v>26.71446525</v>
+        <v>26.3229801</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4014139625633844</v>
+        <v>0.4116643917180886</v>
       </c>
       <c r="T67">
-        <v>2.73375385290947</v>
+        <v>2.81255320598789</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.601829105630974</v>
+        <v>1.577558967666868</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1960988931841501</v>
+        <v>0.1964203994711157</v>
       </c>
       <c r="C68">
-        <v>168.6424188487079</v>
+        <v>163.0965032651259</v>
       </c>
       <c r="D68">
-        <v>441.7404188487079</v>
+        <v>440.7975032651259</v>
       </c>
       <c r="E68">
-        <v>116.398</v>
+        <v>121.001</v>
       </c>
       <c r="F68">
-        <v>303.798</v>
+        <v>308.401</v>
       </c>
       <c r="G68">
         <v>30.7</v>
@@ -6863,28 +6863,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M68">
-        <v>27.34182</v>
+        <v>27.75609</v>
       </c>
       <c r="N68">
-        <v>15.79151333333333</v>
+        <v>15.37724333333333</v>
       </c>
       <c r="O68">
-        <v>0.8685332333333334</v>
+        <v>0.8457483833333332</v>
       </c>
       <c r="P68">
-        <v>14.9229801</v>
+        <v>14.53149495</v>
       </c>
       <c r="Q68">
-        <v>26.3229801</v>
+        <v>25.93149495</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4116643917180886</v>
+        <v>0.4225360590033809</v>
       </c>
       <c r="T68">
-        <v>2.81255320598789</v>
+        <v>2.896128277434699</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.577558967666868</v>
+        <v>1.554013311433034</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1964203994711157</v>
+        <v>0.1967419057580813</v>
       </c>
       <c r="C69">
-        <v>163.0965032651259</v>
+        <v>157.5546045022759</v>
       </c>
       <c r="D69">
-        <v>440.7975032651259</v>
+        <v>439.858604502276</v>
       </c>
       <c r="E69">
-        <v>121.001</v>
+        <v>125.604</v>
       </c>
       <c r="F69">
-        <v>308.401</v>
+        <v>313.004</v>
       </c>
       <c r="G69">
         <v>30.7</v>
@@ -6945,28 +6945,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M69">
-        <v>27.75609</v>
+        <v>28.17036</v>
       </c>
       <c r="N69">
-        <v>15.37724333333333</v>
+        <v>14.96297333333333</v>
       </c>
       <c r="O69">
-        <v>0.8457483833333332</v>
+        <v>0.8229635333333332</v>
       </c>
       <c r="P69">
-        <v>14.53149495</v>
+        <v>14.1400098</v>
       </c>
       <c r="Q69">
-        <v>25.93149495</v>
+        <v>25.5400098</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4225360590033809</v>
+        <v>0.434087205494004</v>
       </c>
       <c r="T69">
-        <v>2.896128277434699</v>
+        <v>2.984926790846933</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.554013311433034</v>
+        <v>1.531160174500195</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1967419057580813</v>
+        <v>0.1970634120450468</v>
       </c>
       <c r="C70">
-        <v>157.5546045022759</v>
+        <v>152.0166969472272</v>
       </c>
       <c r="D70">
-        <v>439.858604502276</v>
+        <v>438.9236969472271</v>
       </c>
       <c r="E70">
-        <v>125.604</v>
+        <v>130.207</v>
       </c>
       <c r="F70">
-        <v>313.004</v>
+        <v>317.607</v>
       </c>
       <c r="G70">
         <v>30.7</v>
@@ -7027,28 +7027,28 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M70">
-        <v>28.17036</v>
+        <v>28.58463</v>
       </c>
       <c r="N70">
-        <v>14.96297333333333</v>
+        <v>14.54870333333334</v>
       </c>
       <c r="O70">
-        <v>0.8229635333333332</v>
+        <v>0.8001786833333334</v>
       </c>
       <c r="P70">
-        <v>14.1400098</v>
+        <v>13.74852465</v>
       </c>
       <c r="Q70">
-        <v>25.5400098</v>
+        <v>25.14852465</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.434087205494004</v>
+        <v>0.4463835872420866</v>
       </c>
       <c r="T70">
-        <v>2.984926790846933</v>
+        <v>3.079454240608344</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.531160174500195</v>
+        <v>1.508969447333526</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1970634120450468</v>
+        <v>0.2358938437390584</v>
       </c>
       <c r="C71">
-        <v>152.0166969472272</v>
+        <v>57.75484057422392</v>
       </c>
       <c r="D71">
-        <v>438.9236969472271</v>
+        <v>349.2648405742239</v>
       </c>
       <c r="E71">
-        <v>130.207</v>
+        <v>134.81</v>
       </c>
       <c r="F71">
-        <v>317.607</v>
+        <v>322.21</v>
       </c>
       <c r="G71">
         <v>30.7</v>
@@ -7109,45 +7109,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M71">
-        <v>28.58463</v>
+        <v>47.300428</v>
       </c>
       <c r="N71">
-        <v>14.54870333333334</v>
+        <v>-4.167094666666671</v>
       </c>
       <c r="O71">
-        <v>0.8001786833333334</v>
+        <v>-0.2291902066666669</v>
       </c>
       <c r="P71">
-        <v>13.74852465</v>
+        <v>-3.937904460000004</v>
       </c>
       <c r="Q71">
-        <v>25.14852465</v>
+        <v>7.462095539999996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4463835872420866</v>
+        <v>0.4609590962880871</v>
       </c>
       <c r="T71">
-        <v>3.079454240608344</v>
+        <v>3.191502298916849</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.055</v>
+        <v>0.0501545849296191</v>
       </c>
       <c r="W71">
-        <v>0.08504999999999999</v>
+        <v>0.1394373069323319</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.508969447333526</v>
+        <v>0.9119015441748927</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2358938437390584</v>
+        <v>0.2369038437390584</v>
       </c>
       <c r="C72">
-        <v>57.75484057422392</v>
+        <v>51.30594631025696</v>
       </c>
       <c r="D72">
-        <v>349.2648405742239</v>
+        <v>347.418946310257</v>
       </c>
       <c r="E72">
-        <v>134.81</v>
+        <v>139.413</v>
       </c>
       <c r="F72">
-        <v>322.21</v>
+        <v>326.813</v>
       </c>
       <c r="G72">
         <v>30.7</v>
@@ -7191,37 +7191,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M72">
-        <v>47.300428</v>
+        <v>47.9761484</v>
       </c>
       <c r="N72">
-        <v>-4.167094666666671</v>
+        <v>-4.842815066666667</v>
       </c>
       <c r="O72">
-        <v>-0.2291902066666669</v>
+        <v>-0.2663548286666667</v>
       </c>
       <c r="P72">
-        <v>-3.937904460000004</v>
+        <v>-4.576460238</v>
       </c>
       <c r="Q72">
-        <v>7.462095539999996</v>
+        <v>6.823539762</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4609590962880871</v>
+        <v>0.4752749271945728</v>
       </c>
       <c r="T72">
-        <v>3.191502298916849</v>
+        <v>3.301554102327775</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.0501545849296191</v>
+        <v>0.04944818232497658</v>
       </c>
       <c r="W72">
-        <v>0.1394373069323319</v>
+        <v>0.1395410068346934</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9119015441748927</v>
+        <v>0.8990578604541196</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2369038437390585</v>
+        <v>0.2379138437390584</v>
       </c>
       <c r="C73">
-        <v>51.30594631025701</v>
+        <v>44.87646088399083</v>
       </c>
       <c r="D73">
-        <v>347.418946310257</v>
+        <v>345.5924608839908</v>
       </c>
       <c r="E73">
-        <v>139.4129999999999</v>
+        <v>144.0159999999999</v>
       </c>
       <c r="F73">
-        <v>326.8129999999999</v>
+        <v>331.4159999999999</v>
       </c>
       <c r="G73">
         <v>30.7</v>
@@ -7273,37 +7273,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M73">
-        <v>47.97614839999999</v>
+        <v>48.6518688</v>
       </c>
       <c r="N73">
-        <v>-4.84281506666666</v>
+        <v>-5.518535466666663</v>
       </c>
       <c r="O73">
-        <v>-0.2663548286666663</v>
+        <v>-0.3035194506666665</v>
       </c>
       <c r="P73">
-        <v>-4.576460237999993</v>
+        <v>-5.215016015999996</v>
       </c>
       <c r="Q73">
-        <v>6.823539762000007</v>
+        <v>6.184983984000004</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4752749271945727</v>
+        <v>0.4906133174515218</v>
       </c>
       <c r="T73">
-        <v>3.301554102327774</v>
+        <v>3.419466748839481</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.04944818232497659</v>
+        <v>0.04876140201490747</v>
       </c>
       <c r="W73">
-        <v>0.1395410068346934</v>
+        <v>0.1396418261842116</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8990578604541197</v>
+        <v>0.8865709457255903</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2379138437390584</v>
+        <v>0.2389238437390585</v>
       </c>
       <c r="C74">
-        <v>44.87646088399083</v>
+        <v>38.46607978212933</v>
       </c>
       <c r="D74">
-        <v>345.5924608839908</v>
+        <v>343.7850797821293</v>
       </c>
       <c r="E74">
-        <v>144.0159999999999</v>
+        <v>148.6189999999999</v>
       </c>
       <c r="F74">
-        <v>331.4159999999999</v>
+        <v>336.0189999999999</v>
       </c>
       <c r="G74">
         <v>30.7</v>
@@ -7355,37 +7355,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M74">
-        <v>48.6518688</v>
+        <v>49.3275892</v>
       </c>
       <c r="N74">
-        <v>-5.518535466666663</v>
+        <v>-6.194255866666666</v>
       </c>
       <c r="O74">
-        <v>-0.3035194506666665</v>
+        <v>-0.3406840726666666</v>
       </c>
       <c r="P74">
-        <v>-5.215016015999996</v>
+        <v>-5.853571793999999</v>
       </c>
       <c r="Q74">
-        <v>6.184983984000004</v>
+        <v>5.546428206000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4906133174515218</v>
+        <v>0.507087884764541</v>
       </c>
       <c r="T74">
-        <v>3.419466748839481</v>
+        <v>3.546113665463165</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.04876140201490747</v>
+        <v>0.04809343760374434</v>
       </c>
       <c r="W74">
-        <v>0.1396418261842116</v>
+        <v>0.1397398833597704</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8865709457255903</v>
+        <v>0.8744261382498971</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2389238437390585</v>
+        <v>0.2399338437390584</v>
       </c>
       <c r="C75">
-        <v>38.46607978212933</v>
+        <v>32.07450482841512</v>
       </c>
       <c r="D75">
-        <v>343.7850797821293</v>
+        <v>341.9965048284151</v>
       </c>
       <c r="E75">
-        <v>148.6189999999999</v>
+        <v>153.222</v>
       </c>
       <c r="F75">
-        <v>336.0189999999999</v>
+        <v>340.622</v>
       </c>
       <c r="G75">
         <v>30.7</v>
@@ -7437,37 +7437,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M75">
-        <v>49.3275892</v>
+        <v>50.0033096</v>
       </c>
       <c r="N75">
-        <v>-6.194255866666666</v>
+        <v>-6.869976266666669</v>
       </c>
       <c r="O75">
-        <v>-0.3406840726666666</v>
+        <v>-0.3778486946666668</v>
       </c>
       <c r="P75">
-        <v>-5.853571793999999</v>
+        <v>-6.492127572000002</v>
       </c>
       <c r="Q75">
-        <v>5.546428206000002</v>
+        <v>4.907872427999998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.507087884764541</v>
+        <v>0.5248297264862541</v>
       </c>
       <c r="T75">
-        <v>3.546113665463165</v>
+        <v>3.682502652596364</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.04809343760374434</v>
+        <v>0.04744352628477482</v>
       </c>
       <c r="W75">
-        <v>0.1397398833597704</v>
+        <v>0.1398352903413951</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8744261382498971</v>
+        <v>0.8626095688140877</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2399338437390584</v>
+        <v>0.2409438437390584</v>
       </c>
       <c r="C76">
-        <v>32.07450482841512</v>
+        <v>25.70144401963762</v>
       </c>
       <c r="D76">
-        <v>341.9965048284151</v>
+        <v>340.2264440196376</v>
       </c>
       <c r="E76">
-        <v>153.222</v>
+        <v>157.825</v>
       </c>
       <c r="F76">
-        <v>340.622</v>
+        <v>345.225</v>
       </c>
       <c r="G76">
         <v>30.7</v>
@@ -7519,37 +7519,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M76">
-        <v>50.0033096</v>
+        <v>50.67903</v>
       </c>
       <c r="N76">
-        <v>-6.869976266666669</v>
+        <v>-7.545696666666664</v>
       </c>
       <c r="O76">
-        <v>-0.3778486946666668</v>
+        <v>-0.4150133166666666</v>
       </c>
       <c r="P76">
-        <v>-6.492127572000002</v>
+        <v>-7.130683349999998</v>
       </c>
       <c r="Q76">
-        <v>4.907872427999998</v>
+        <v>4.269316650000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5248297264862541</v>
+        <v>0.5439909155457043</v>
       </c>
       <c r="T76">
-        <v>3.682502652596364</v>
+        <v>3.829802758700219</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.04744352628477482</v>
+        <v>0.04681094593431116</v>
       </c>
       <c r="W76">
-        <v>0.1398352903413951</v>
+        <v>0.1399281531368431</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8626095688140877</v>
+        <v>0.8511081078965665</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2409438437390584</v>
+        <v>0.2419538437390584</v>
       </c>
       <c r="C77">
-        <v>25.70144401963762</v>
+        <v>19.34661136670763</v>
       </c>
       <c r="D77">
-        <v>340.2264440196376</v>
+        <v>338.4746113667076</v>
       </c>
       <c r="E77">
-        <v>157.825</v>
+        <v>162.428</v>
       </c>
       <c r="F77">
-        <v>345.225</v>
+        <v>349.828</v>
       </c>
       <c r="G77">
         <v>30.7</v>
@@ -7601,37 +7601,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M77">
-        <v>50.67903</v>
+        <v>51.3547504</v>
       </c>
       <c r="N77">
-        <v>-7.545696666666664</v>
+        <v>-8.221417066666667</v>
       </c>
       <c r="O77">
-        <v>-0.4150133166666666</v>
+        <v>-0.4521779386666667</v>
       </c>
       <c r="P77">
-        <v>-7.130683349999998</v>
+        <v>-7.769239128000001</v>
       </c>
       <c r="Q77">
-        <v>4.269316650000002</v>
+        <v>3.630760872</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5439909155457043</v>
+        <v>0.5647488703601086</v>
       </c>
       <c r="T77">
-        <v>3.829802758700219</v>
+        <v>3.98937787364606</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.04681094593431116</v>
+        <v>0.04619501243517549</v>
       </c>
       <c r="W77">
-        <v>0.1399281531368431</v>
+        <v>0.1400185721745162</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8511081078965665</v>
+        <v>0.8399093170031906</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2419538437390584</v>
+        <v>0.2429638437390584</v>
       </c>
       <c r="C78">
-        <v>19.34661136670763</v>
+        <v>13.00972674061546</v>
       </c>
       <c r="D78">
-        <v>338.4746113667076</v>
+        <v>336.7407267406155</v>
       </c>
       <c r="E78">
-        <v>162.428</v>
+        <v>167.031</v>
       </c>
       <c r="F78">
-        <v>349.828</v>
+        <v>354.431</v>
       </c>
       <c r="G78">
         <v>30.7</v>
@@ -7683,37 +7683,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M78">
-        <v>51.3547504</v>
+        <v>52.0304708</v>
       </c>
       <c r="N78">
-        <v>-8.221417066666667</v>
+        <v>-8.89713746666667</v>
       </c>
       <c r="O78">
-        <v>-0.4521779386666667</v>
+        <v>-0.4893425606666669</v>
       </c>
       <c r="P78">
-        <v>-7.769239128000001</v>
+        <v>-8.407794906000003</v>
       </c>
       <c r="Q78">
-        <v>3.630760872</v>
+        <v>2.992205093999997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5647488703601086</v>
+        <v>0.5873118647235918</v>
       </c>
       <c r="T78">
-        <v>3.98937787364606</v>
+        <v>4.162829085543716</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.04619501243517549</v>
+        <v>0.04559507720874463</v>
       </c>
       <c r="W78">
-        <v>0.1400185721745162</v>
+        <v>0.1401066426657563</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8399093170031906</v>
+        <v>0.829001403795357</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2429638437390584</v>
+        <v>0.2439738437390584</v>
       </c>
       <c r="C79">
-        <v>13.00972674061546</v>
+        <v>6.690515723101669</v>
       </c>
       <c r="D79">
-        <v>336.7407267406155</v>
+        <v>335.0245157231017</v>
       </c>
       <c r="E79">
-        <v>167.031</v>
+        <v>171.634</v>
       </c>
       <c r="F79">
-        <v>354.431</v>
+        <v>359.034</v>
       </c>
       <c r="G79">
         <v>30.7</v>
@@ -7765,37 +7765,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M79">
-        <v>52.0304708</v>
+        <v>52.70619120000001</v>
       </c>
       <c r="N79">
-        <v>-8.89713746666667</v>
+        <v>-9.572857866666673</v>
       </c>
       <c r="O79">
-        <v>-0.4893425606666669</v>
+        <v>-0.5265071826666671</v>
       </c>
       <c r="P79">
-        <v>-8.407794906000003</v>
+        <v>-9.046350684000007</v>
       </c>
       <c r="Q79">
-        <v>2.992205093999997</v>
+        <v>2.353649315999993</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5873118647235918</v>
+        <v>0.6119260403928459</v>
       </c>
       <c r="T79">
-        <v>4.162829085543716</v>
+        <v>4.352048589432068</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.04559507720874463</v>
+        <v>0.04501052493683765</v>
       </c>
       <c r="W79">
-        <v>0.1401066426657563</v>
+        <v>0.1401924549392722</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.829001403795357</v>
+        <v>0.8183731806697754</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2439738437390584</v>
+        <v>0.2449838437390585</v>
       </c>
       <c r="C80">
-        <v>6.690515723101669</v>
+        <v>0.3887094618688138</v>
       </c>
       <c r="D80">
-        <v>335.0245157231017</v>
+        <v>333.3257094618688</v>
       </c>
       <c r="E80">
-        <v>171.634</v>
+        <v>176.237</v>
       </c>
       <c r="F80">
-        <v>359.034</v>
+        <v>363.637</v>
       </c>
       <c r="G80">
         <v>30.7</v>
@@ -7847,37 +7847,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M80">
-        <v>52.70619120000001</v>
+        <v>53.3819116</v>
       </c>
       <c r="N80">
-        <v>-9.572857866666673</v>
+        <v>-10.24857826666667</v>
       </c>
       <c r="O80">
-        <v>-0.5265071826666671</v>
+        <v>-0.5636718046666668</v>
       </c>
       <c r="P80">
-        <v>-9.046350684000007</v>
+        <v>-9.684906462000002</v>
       </c>
       <c r="Q80">
-        <v>2.353649315999993</v>
+        <v>1.715093537999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6119260403928459</v>
+        <v>0.6388844232686959</v>
       </c>
       <c r="T80">
-        <v>4.352048589432068</v>
+        <v>4.559288998452643</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.04501052493683765</v>
+        <v>0.04444077145662452</v>
       </c>
       <c r="W80">
-        <v>0.1401924549392722</v>
+        <v>0.1402760947501675</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8183731806697754</v>
+        <v>0.8080140264840822</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2449838437390585</v>
+        <v>0.2904125412755715</v>
       </c>
       <c r="C81">
-        <v>0.3887094618688138</v>
+        <v>-66.11852797961137</v>
       </c>
       <c r="D81">
-        <v>333.3257094618688</v>
+        <v>271.4214720203886</v>
       </c>
       <c r="E81">
-        <v>176.237</v>
+        <v>180.84</v>
       </c>
       <c r="F81">
-        <v>363.637</v>
+        <v>368.24</v>
       </c>
       <c r="G81">
         <v>30.7</v>
@@ -7929,45 +7929,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M81">
-        <v>53.3819116</v>
+        <v>73.942592</v>
       </c>
       <c r="N81">
-        <v>-10.24857826666667</v>
+        <v>-30.80925866666667</v>
       </c>
       <c r="O81">
-        <v>-0.5636718046666668</v>
+        <v>-1.694509226666667</v>
       </c>
       <c r="P81">
-        <v>-9.684906462000002</v>
+        <v>-29.11474944</v>
       </c>
       <c r="Q81">
-        <v>1.715093537999998</v>
+        <v>-17.71474944000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6388844232686959</v>
+        <v>0.6746321321146957</v>
       </c>
       <c r="T81">
-        <v>4.559288998452643</v>
+        <v>4.834096646853173</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04444077145662452</v>
+        <v>0.03208344837753771</v>
       </c>
       <c r="W81">
-        <v>0.1402760947501675</v>
+        <v>0.1943576435657904</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8080140264840822</v>
+        <v>0.5833354250461402</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2904125412755715</v>
+        <v>0.2919625412755714</v>
       </c>
       <c r="C82">
-        <v>-66.11852797961137</v>
+        <v>-72.43057469098983</v>
       </c>
       <c r="D82">
-        <v>271.4214720203886</v>
+        <v>269.7124253090101</v>
       </c>
       <c r="E82">
-        <v>180.84</v>
+        <v>185.443</v>
       </c>
       <c r="F82">
-        <v>368.24</v>
+        <v>372.843</v>
       </c>
       <c r="G82">
         <v>30.7</v>
@@ -8011,37 +8011,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M82">
-        <v>73.942592</v>
+        <v>74.8668744</v>
       </c>
       <c r="N82">
-        <v>-30.80925866666667</v>
+        <v>-31.73354106666667</v>
       </c>
       <c r="O82">
-        <v>-1.694509226666667</v>
+        <v>-1.745344758666667</v>
       </c>
       <c r="P82">
-        <v>-29.11474944</v>
+        <v>-29.988196308</v>
       </c>
       <c r="Q82">
-        <v>-17.71474944000001</v>
+        <v>-18.588196308</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6746321321146957</v>
+        <v>0.7077285601207322</v>
       </c>
       <c r="T82">
-        <v>4.834096646853173</v>
+        <v>5.088522786161234</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.03208344837753771</v>
+        <v>0.03168735642225948</v>
       </c>
       <c r="W82">
-        <v>0.1943576435657904</v>
+        <v>0.1944371788304103</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5833354250461402</v>
+        <v>0.5761337531319903</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2919625412755714</v>
+        <v>0.2935125412755715</v>
       </c>
       <c r="C83">
-        <v>-72.43057469098983</v>
+        <v>-78.72123352762469</v>
       </c>
       <c r="D83">
-        <v>269.7124253090101</v>
+        <v>268.0247664723753</v>
       </c>
       <c r="E83">
-        <v>185.443</v>
+        <v>190.046</v>
       </c>
       <c r="F83">
-        <v>372.843</v>
+        <v>377.446</v>
       </c>
       <c r="G83">
         <v>30.7</v>
@@ -8093,37 +8093,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M83">
-        <v>74.8668744</v>
+        <v>75.7911568</v>
       </c>
       <c r="N83">
-        <v>-31.73354106666667</v>
+        <v>-32.65782346666666</v>
       </c>
       <c r="O83">
-        <v>-1.745344758666667</v>
+        <v>-1.796180290666666</v>
       </c>
       <c r="P83">
-        <v>-29.988196308</v>
+        <v>-30.861643176</v>
       </c>
       <c r="Q83">
-        <v>-18.588196308</v>
+        <v>-19.461643176</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7077285601207322</v>
+        <v>0.7445023690163285</v>
       </c>
       <c r="T83">
-        <v>5.088522786161234</v>
+        <v>5.371218496503525</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03168735642225948</v>
+        <v>0.03130092524637826</v>
       </c>
       <c r="W83">
-        <v>0.1944371788304103</v>
+        <v>0.1945147742105272</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5761337531319903</v>
+        <v>0.5691077317523321</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2935125412755715</v>
+        <v>0.2950625412755715</v>
       </c>
       <c r="C84">
-        <v>-78.72123352762469</v>
+        <v>-84.99090348094461</v>
       </c>
       <c r="D84">
-        <v>268.0247664723753</v>
+        <v>266.3580965190554</v>
       </c>
       <c r="E84">
-        <v>190.046</v>
+        <v>194.649</v>
       </c>
       <c r="F84">
-        <v>377.446</v>
+        <v>382.049</v>
       </c>
       <c r="G84">
         <v>30.7</v>
@@ -8175,37 +8175,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M84">
-        <v>75.7911568</v>
+        <v>76.71543919999999</v>
       </c>
       <c r="N84">
-        <v>-32.65782346666666</v>
+        <v>-33.58210586666666</v>
       </c>
       <c r="O84">
-        <v>-1.796180290666666</v>
+        <v>-1.847015822666666</v>
       </c>
       <c r="P84">
-        <v>-30.861643176</v>
+        <v>-31.73509004399999</v>
       </c>
       <c r="Q84">
-        <v>-19.461643176</v>
+        <v>-20.33509004399999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7445023690163285</v>
+        <v>0.7856025083702303</v>
       </c>
       <c r="T84">
-        <v>5.371218496503525</v>
+        <v>5.687172525709616</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03130092524637826</v>
+        <v>0.03092380566509659</v>
       </c>
       <c r="W84">
-        <v>0.1945147742105272</v>
+        <v>0.1945904998224486</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5691077317523321</v>
+        <v>0.5622510120926654</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2950625412755715</v>
+        <v>0.2966125412755715</v>
       </c>
       <c r="C85">
-        <v>-84.99090348094461</v>
+        <v>-91.2399736794477</v>
       </c>
       <c r="D85">
-        <v>266.3580965190554</v>
+        <v>264.7120263205523</v>
       </c>
       <c r="E85">
-        <v>194.649</v>
+        <v>199.252</v>
       </c>
       <c r="F85">
-        <v>382.049</v>
+        <v>386.652</v>
       </c>
       <c r="G85">
         <v>30.7</v>
@@ -8257,37 +8257,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M85">
-        <v>76.71543919999999</v>
+        <v>77.6397216</v>
       </c>
       <c r="N85">
-        <v>-33.58210586666666</v>
+        <v>-34.50638826666667</v>
       </c>
       <c r="O85">
-        <v>-1.847015822666666</v>
+        <v>-1.897851354666667</v>
       </c>
       <c r="P85">
-        <v>-31.73509004399999</v>
+        <v>-32.60853691200001</v>
       </c>
       <c r="Q85">
-        <v>-20.33509004399999</v>
+        <v>-21.20853691200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7856025083702303</v>
+        <v>0.8318401651433698</v>
       </c>
       <c r="T85">
-        <v>5.687172525709616</v>
+        <v>6.042620808566468</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03092380566509659</v>
+        <v>0.03055566512146449</v>
       </c>
       <c r="W85">
-        <v>0.1945904998224486</v>
+        <v>0.1946644224436099</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5622510120926654</v>
+        <v>0.5555575476629908</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2966125412755715</v>
+        <v>0.2981625412755714</v>
       </c>
       <c r="C86">
-        <v>-91.23997367944764</v>
+        <v>-97.46882369158874</v>
       </c>
       <c r="D86">
-        <v>264.7120263205523</v>
+        <v>263.0861763084112</v>
       </c>
       <c r="E86">
-        <v>199.2519999999999</v>
+        <v>203.8549999999999</v>
       </c>
       <c r="F86">
-        <v>386.6519999999999</v>
+        <v>391.2549999999999</v>
       </c>
       <c r="G86">
         <v>30.7</v>
@@ -8339,37 +8339,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M86">
-        <v>77.63972159999999</v>
+        <v>78.564004</v>
       </c>
       <c r="N86">
-        <v>-34.50638826666665</v>
+        <v>-35.43067066666666</v>
       </c>
       <c r="O86">
-        <v>-1.897851354666666</v>
+        <v>-1.948686886666666</v>
       </c>
       <c r="P86">
-        <v>-32.60853691199999</v>
+        <v>-33.48198378</v>
       </c>
       <c r="Q86">
-        <v>-21.20853691199999</v>
+        <v>-22.08198378</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8318401651433692</v>
+        <v>0.8842428428195939</v>
       </c>
       <c r="T86">
-        <v>6.042620808566464</v>
+        <v>6.445462195804228</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03055566512146449</v>
+        <v>0.03019618670827079</v>
       </c>
       <c r="W86">
-        <v>0.1946644224436099</v>
+        <v>0.1947366057089792</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5555575476629908</v>
+        <v>0.5490215765140144</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2981625412755714</v>
+        <v>0.2997125412755715</v>
       </c>
       <c r="C87">
-        <v>-97.46882369158874</v>
+        <v>-103.677823817575</v>
       </c>
       <c r="D87">
-        <v>263.0861763084112</v>
+        <v>261.480176182425</v>
       </c>
       <c r="E87">
-        <v>203.8549999999999</v>
+        <v>208.4579999999999</v>
       </c>
       <c r="F87">
-        <v>391.2549999999999</v>
+        <v>395.8579999999999</v>
       </c>
       <c r="G87">
         <v>30.7</v>
@@ -8421,37 +8421,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M87">
-        <v>78.564004</v>
+        <v>79.48828639999999</v>
       </c>
       <c r="N87">
-        <v>-35.43067066666666</v>
+        <v>-36.35495306666666</v>
       </c>
       <c r="O87">
-        <v>-1.948686886666666</v>
+        <v>-1.999522418666666</v>
       </c>
       <c r="P87">
-        <v>-33.48198378</v>
+        <v>-34.355430648</v>
       </c>
       <c r="Q87">
-        <v>-22.08198378</v>
+        <v>-22.955430648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8842428428195939</v>
+        <v>0.9441316173067079</v>
       </c>
       <c r="T87">
-        <v>6.445462195804228</v>
+        <v>6.905852352647389</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03019618670827079</v>
+        <v>0.02984506825817462</v>
       </c>
       <c r="W87">
-        <v>0.1947366057089792</v>
+        <v>0.1948071102937586</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5490215765140144</v>
+        <v>0.5426376046940841</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2997125412755715</v>
+        <v>0.3012625412755714</v>
       </c>
       <c r="C88">
-        <v>-103.677823817575</v>
+        <v>-109.867335370537</v>
       </c>
       <c r="D88">
-        <v>261.480176182425</v>
+        <v>259.8936646294629</v>
       </c>
       <c r="E88">
-        <v>208.4579999999999</v>
+        <v>213.061</v>
       </c>
       <c r="F88">
-        <v>395.8579999999999</v>
+        <v>400.461</v>
       </c>
       <c r="G88">
         <v>30.7</v>
@@ -8503,37 +8503,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M88">
-        <v>79.48828639999999</v>
+        <v>80.41256879999999</v>
       </c>
       <c r="N88">
-        <v>-36.35495306666666</v>
+        <v>-37.27923546666666</v>
       </c>
       <c r="O88">
-        <v>-1.999522418666666</v>
+        <v>-2.050357950666666</v>
       </c>
       <c r="P88">
-        <v>-34.355430648</v>
+        <v>-35.22887751599999</v>
       </c>
       <c r="Q88">
-        <v>-22.955430648</v>
+        <v>-23.82887751599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9441316173067079</v>
+        <v>1.013234049407224</v>
       </c>
       <c r="T88">
-        <v>6.905852352647389</v>
+        <v>7.437071764389495</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.02984506825817462</v>
+        <v>0.02950202149658641</v>
       </c>
       <c r="W88">
-        <v>0.1948071102937586</v>
+        <v>0.1948759940834854</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5426376046940841</v>
+        <v>0.5364003908470256</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3012625412755714</v>
+        <v>0.3028125412755715</v>
       </c>
       <c r="C89">
-        <v>-109.867335370537</v>
+        <v>-116.037710947528</v>
       </c>
       <c r="D89">
-        <v>259.8936646294629</v>
+        <v>258.326289052472</v>
       </c>
       <c r="E89">
-        <v>213.061</v>
+        <v>217.664</v>
       </c>
       <c r="F89">
-        <v>400.461</v>
+        <v>405.064</v>
       </c>
       <c r="G89">
         <v>30.7</v>
@@ -8585,37 +8585,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M89">
-        <v>80.41256879999999</v>
+        <v>81.3368512</v>
       </c>
       <c r="N89">
-        <v>-37.27923546666666</v>
+        <v>-38.20351786666667</v>
       </c>
       <c r="O89">
-        <v>-2.050357950666666</v>
+        <v>-2.101193482666667</v>
       </c>
       <c r="P89">
-        <v>-35.22887751599999</v>
+        <v>-36.102324384</v>
       </c>
       <c r="Q89">
-        <v>-23.82887751599999</v>
+        <v>-24.702324384</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.013234049407224</v>
+        <v>1.093853553524493</v>
       </c>
       <c r="T89">
-        <v>7.437071764389495</v>
+        <v>8.056827744755289</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.02950202149658641</v>
+        <v>0.02916677125230701</v>
       </c>
       <c r="W89">
-        <v>0.1948759940834854</v>
+        <v>0.1949433123325368</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5364003908470256</v>
+        <v>0.5303049318601276</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3028125412755715</v>
+        <v>0.3043625412755714</v>
       </c>
       <c r="C90">
-        <v>-116.037710947528</v>
+        <v>-122.1892946907724</v>
       </c>
       <c r="D90">
-        <v>258.326289052472</v>
+        <v>256.7777053092276</v>
       </c>
       <c r="E90">
-        <v>217.664</v>
+        <v>222.267</v>
       </c>
       <c r="F90">
-        <v>405.064</v>
+        <v>409.667</v>
       </c>
       <c r="G90">
         <v>30.7</v>
@@ -8667,37 +8667,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M90">
-        <v>81.3368512</v>
+        <v>82.26113359999999</v>
       </c>
       <c r="N90">
-        <v>-38.20351786666667</v>
+        <v>-39.12780026666666</v>
       </c>
       <c r="O90">
-        <v>-2.101193482666667</v>
+        <v>-2.152029014666666</v>
       </c>
       <c r="P90">
-        <v>-36.102324384</v>
+        <v>-36.97577125199999</v>
       </c>
       <c r="Q90">
-        <v>-24.702324384</v>
+        <v>-25.575771252</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.093853553524493</v>
+        <v>1.189131149299447</v>
       </c>
       <c r="T90">
-        <v>8.056827744755289</v>
+        <v>8.78926663064213</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.02916677125230701</v>
+        <v>0.02883905472138222</v>
       </c>
       <c r="W90">
-        <v>0.1949433123325368</v>
+        <v>0.1950091178119464</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5303049318601276</v>
+        <v>0.5243464494796768</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3043625412755714</v>
+        <v>0.3059125412755715</v>
       </c>
       <c r="C91">
-        <v>-122.1892946907724</v>
+        <v>-128.3224225395779</v>
       </c>
       <c r="D91">
-        <v>256.7777053092276</v>
+        <v>255.2475774604221</v>
       </c>
       <c r="E91">
-        <v>222.267</v>
+        <v>226.87</v>
       </c>
       <c r="F91">
-        <v>409.667</v>
+        <v>414.27</v>
       </c>
       <c r="G91">
         <v>30.7</v>
@@ -8749,37 +8749,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M91">
-        <v>82.26113359999999</v>
+        <v>83.185416</v>
       </c>
       <c r="N91">
-        <v>-39.12780026666666</v>
+        <v>-40.05208266666667</v>
       </c>
       <c r="O91">
-        <v>-2.152029014666666</v>
+        <v>-2.202864546666667</v>
       </c>
       <c r="P91">
-        <v>-36.97577125199999</v>
+        <v>-37.84921812</v>
       </c>
       <c r="Q91">
-        <v>-25.575771252</v>
+        <v>-26.44921812</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.189131149299447</v>
+        <v>1.303464264229392</v>
       </c>
       <c r="T91">
-        <v>8.78926663064213</v>
+        <v>9.668193293706347</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.02883905472138222</v>
+        <v>0.02851862078003353</v>
       </c>
       <c r="W91">
-        <v>0.1950091178119464</v>
+        <v>0.1950734609473693</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5243464494796768</v>
+        <v>0.5185203778187913</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3059125412755715</v>
+        <v>0.3074625412755715</v>
       </c>
       <c r="C92">
-        <v>-128.3224225395779</v>
+        <v>-134.4374224732902</v>
       </c>
       <c r="D92">
-        <v>255.2475774604221</v>
+        <v>253.7355775267098</v>
       </c>
       <c r="E92">
-        <v>226.87</v>
+        <v>231.473</v>
       </c>
       <c r="F92">
-        <v>414.27</v>
+        <v>418.873</v>
       </c>
       <c r="G92">
         <v>30.7</v>
@@ -8831,37 +8831,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M92">
-        <v>83.185416</v>
+        <v>84.1096984</v>
       </c>
       <c r="N92">
-        <v>-40.05208266666667</v>
+        <v>-40.97636506666667</v>
       </c>
       <c r="O92">
-        <v>-2.202864546666667</v>
+        <v>-2.253700078666667</v>
       </c>
       <c r="P92">
-        <v>-37.84921812</v>
+        <v>-38.722664988</v>
       </c>
       <c r="Q92">
-        <v>-26.44921812</v>
+        <v>-27.322664988</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.303464264229392</v>
+        <v>1.443204738032657</v>
       </c>
       <c r="T92">
-        <v>9.668193293706347</v>
+        <v>10.74243699300705</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.02851862078003353</v>
+        <v>0.0282052293428903</v>
       </c>
       <c r="W92">
-        <v>0.1950734609473693</v>
+        <v>0.1951363899479476</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5185203778187913</v>
+        <v>0.5128223516889145</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3074625412755715</v>
+        <v>0.3090125412755714</v>
       </c>
       <c r="C93">
-        <v>-134.4374224732902</v>
+        <v>-140.5346147456661</v>
       </c>
       <c r="D93">
-        <v>253.7355775267098</v>
+        <v>252.2413852543339</v>
       </c>
       <c r="E93">
-        <v>231.473</v>
+        <v>236.076</v>
       </c>
       <c r="F93">
-        <v>418.873</v>
+        <v>423.476</v>
       </c>
       <c r="G93">
         <v>30.7</v>
@@ -8913,37 +8913,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M93">
-        <v>84.1096984</v>
+        <v>85.03398080000001</v>
       </c>
       <c r="N93">
-        <v>-40.97636506666667</v>
+        <v>-41.90064746666668</v>
       </c>
       <c r="O93">
-        <v>-2.253700078666667</v>
+        <v>-2.304535610666667</v>
       </c>
       <c r="P93">
-        <v>-38.722664988</v>
+        <v>-39.59611185600001</v>
       </c>
       <c r="Q93">
-        <v>-27.322664988</v>
+        <v>-28.19611185600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.443204738032657</v>
+        <v>1.61788033028674</v>
       </c>
       <c r="T93">
-        <v>10.74243699300705</v>
+        <v>12.08524161713294</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0282052293428903</v>
+        <v>0.02789865076307627</v>
       </c>
       <c r="W93">
-        <v>0.1951363899479476</v>
+        <v>0.1951979509267743</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5128223516889145</v>
+        <v>0.5072481956922958</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3090125412755714</v>
+        <v>0.3105625412755715</v>
       </c>
       <c r="C94">
-        <v>-140.5346147456661</v>
+        <v>-146.6143121110132</v>
       </c>
       <c r="D94">
-        <v>252.2413852543339</v>
+        <v>250.7646878889868</v>
       </c>
       <c r="E94">
-        <v>236.076</v>
+        <v>240.679</v>
       </c>
       <c r="F94">
-        <v>423.476</v>
+        <v>428.079</v>
       </c>
       <c r="G94">
         <v>30.7</v>
@@ -8995,37 +8995,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M94">
-        <v>85.03398080000001</v>
+        <v>85.9582632</v>
       </c>
       <c r="N94">
-        <v>-41.90064746666668</v>
+        <v>-42.82492986666667</v>
       </c>
       <c r="O94">
-        <v>-2.304535610666667</v>
+        <v>-2.355371142666667</v>
       </c>
       <c r="P94">
-        <v>-39.59611185600001</v>
+        <v>-40.469558724</v>
       </c>
       <c r="Q94">
-        <v>-28.19611185600001</v>
+        <v>-29.069558724</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.61788033028674</v>
+        <v>1.842463234613417</v>
       </c>
       <c r="T94">
-        <v>12.08524161713294</v>
+        <v>13.81170470529479</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.02789865076307627</v>
+        <v>0.02759866527100019</v>
       </c>
       <c r="W94">
-        <v>0.1951979509267743</v>
+        <v>0.1952581880135832</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5072481956922958</v>
+        <v>0.5017939140181852</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3105625412755715</v>
+        <v>0.3455043004517883</v>
       </c>
       <c r="C95">
-        <v>-146.6143121110132</v>
+        <v>-180.4533268125294</v>
       </c>
       <c r="D95">
-        <v>250.7646878889868</v>
+        <v>221.5286731874705</v>
       </c>
       <c r="E95">
-        <v>240.679</v>
+        <v>245.282</v>
       </c>
       <c r="F95">
-        <v>428.079</v>
+        <v>432.682</v>
       </c>
       <c r="G95">
         <v>30.7</v>
@@ -9077,45 +9077,45 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M95">
-        <v>85.9582632</v>
+        <v>102.0264156</v>
       </c>
       <c r="N95">
-        <v>-42.82492986666667</v>
+        <v>-58.89308226666666</v>
       </c>
       <c r="O95">
-        <v>-2.355371142666667</v>
+        <v>-3.239119524666666</v>
       </c>
       <c r="P95">
-        <v>-40.469558724</v>
+        <v>-55.65396274199999</v>
       </c>
       <c r="Q95">
-        <v>-29.069558724</v>
+        <v>-44.25396274199999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.842463234613417</v>
+        <v>2.150103093319268</v>
       </c>
       <c r="T95">
-        <v>13.81170470529479</v>
+        <v>16.17666147747367</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02759866527100019</v>
+        <v>0.02325214817537247</v>
       </c>
       <c r="W95">
-        <v>0.1952581880135832</v>
+        <v>0.2303171434602472</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5017939140181852</v>
+        <v>0.4227663304613176</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3455043004517883</v>
+        <v>0.3474043004517883</v>
       </c>
       <c r="C96">
-        <v>-180.4533268125294</v>
+        <v>-186.4518787938033</v>
       </c>
       <c r="D96">
-        <v>221.5286731874705</v>
+        <v>220.1331212061967</v>
       </c>
       <c r="E96">
-        <v>245.282</v>
+        <v>249.885</v>
       </c>
       <c r="F96">
-        <v>432.682</v>
+        <v>437.285</v>
       </c>
       <c r="G96">
         <v>30.7</v>
@@ -9159,37 +9159,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M96">
-        <v>102.0264156</v>
+        <v>103.111803</v>
       </c>
       <c r="N96">
-        <v>-58.89308226666666</v>
+        <v>-59.97846966666666</v>
       </c>
       <c r="O96">
-        <v>-3.239119524666666</v>
+        <v>-3.298815831666666</v>
       </c>
       <c r="P96">
-        <v>-55.65396274199999</v>
+        <v>-56.679653835</v>
       </c>
       <c r="Q96">
-        <v>-44.25396274199999</v>
+        <v>-45.279653835</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.150103093319268</v>
+        <v>2.570963711983122</v>
       </c>
       <c r="T96">
-        <v>16.17666147747367</v>
+        <v>19.41199377296841</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02325214817537247</v>
+        <v>0.02300738872089486</v>
       </c>
       <c r="W96">
-        <v>0.2303171434602472</v>
+        <v>0.230374857739613</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4227663304613176</v>
+        <v>0.4183161585617249</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3474043004517883</v>
+        <v>0.3493043004517883</v>
       </c>
       <c r="C97">
-        <v>-186.4518787938033</v>
+        <v>-192.4329578841792</v>
       </c>
       <c r="D97">
-        <v>220.1331212061967</v>
+        <v>218.7550421158208</v>
       </c>
       <c r="E97">
-        <v>249.885</v>
+        <v>254.488</v>
       </c>
       <c r="F97">
-        <v>437.285</v>
+        <v>441.888</v>
       </c>
       <c r="G97">
         <v>30.7</v>
@@ -9241,37 +9241,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M97">
-        <v>103.111803</v>
+        <v>104.1971904</v>
       </c>
       <c r="N97">
-        <v>-59.97846966666666</v>
+        <v>-61.06385706666666</v>
       </c>
       <c r="O97">
-        <v>-3.298815831666666</v>
+        <v>-3.358512138666666</v>
       </c>
       <c r="P97">
-        <v>-56.679653835</v>
+        <v>-57.705344928</v>
       </c>
       <c r="Q97">
-        <v>-45.279653835</v>
+        <v>-46.305344928</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.570963711983122</v>
+        <v>3.202254639978904</v>
       </c>
       <c r="T97">
-        <v>19.41199377296841</v>
+        <v>24.26499221621052</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02300738872089486</v>
+        <v>0.02276772842171888</v>
       </c>
       <c r="W97">
-        <v>0.230374857739613</v>
+        <v>0.2304313696381587</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4183161585617249</v>
+        <v>0.4139586985767069</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3493043004517883</v>
+        <v>0.3512043004517883</v>
       </c>
       <c r="C98">
-        <v>-192.4329578841792</v>
+        <v>-198.3968901939246</v>
       </c>
       <c r="D98">
-        <v>218.7550421158208</v>
+        <v>217.3941098060753</v>
       </c>
       <c r="E98">
-        <v>254.4879999999999</v>
+        <v>259.0909999999999</v>
       </c>
       <c r="F98">
-        <v>441.8879999999999</v>
+        <v>446.4909999999999</v>
       </c>
       <c r="G98">
         <v>30.7</v>
@@ -9323,37 +9323,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M98">
-        <v>104.1971904</v>
+        <v>105.2825778</v>
       </c>
       <c r="N98">
-        <v>-61.06385706666665</v>
+        <v>-62.14924446666665</v>
       </c>
       <c r="O98">
-        <v>-3.358512138666666</v>
+        <v>-3.418208445666666</v>
       </c>
       <c r="P98">
-        <v>-57.70534492799998</v>
+        <v>-58.73103602099999</v>
       </c>
       <c r="Q98">
-        <v>-46.30534492799998</v>
+        <v>-47.33103602099999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.202254639978895</v>
+        <v>4.254406186638528</v>
       </c>
       <c r="T98">
-        <v>24.26499221621046</v>
+        <v>32.35332295494729</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02276772842171888</v>
+        <v>0.02253300957201044</v>
       </c>
       <c r="W98">
-        <v>0.2304313696381587</v>
+        <v>0.23048671634292</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.413958698576707</v>
+        <v>0.4096910831274625</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3512043004517883</v>
+        <v>0.3531043004517882</v>
       </c>
       <c r="C99">
-        <v>-198.3968901939246</v>
+        <v>-204.3439937682133</v>
       </c>
       <c r="D99">
-        <v>217.3941098060753</v>
+        <v>216.0500062317867</v>
       </c>
       <c r="E99">
-        <v>259.0909999999999</v>
+        <v>263.694</v>
       </c>
       <c r="F99">
-        <v>446.4909999999999</v>
+        <v>451.0939999999999</v>
       </c>
       <c r="G99">
         <v>30.7</v>
@@ -9405,37 +9405,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M99">
-        <v>105.2825778</v>
+        <v>106.3679652</v>
       </c>
       <c r="N99">
-        <v>-62.14924446666665</v>
+        <v>-63.23463186666665</v>
       </c>
       <c r="O99">
-        <v>-3.418208445666666</v>
+        <v>-3.477904752666666</v>
       </c>
       <c r="P99">
-        <v>-58.73103602099999</v>
+        <v>-59.75672711399999</v>
       </c>
       <c r="Q99">
-        <v>-47.33103602099999</v>
+        <v>-48.35672711399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.254406186638528</v>
+        <v>6.35870927995779</v>
       </c>
       <c r="T99">
-        <v>32.35332295494729</v>
+        <v>48.52998443242091</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02253300957201044</v>
+        <v>0.02230308090290829</v>
       </c>
       <c r="W99">
-        <v>0.23048671634292</v>
+        <v>0.2305409335230942</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4096910831274625</v>
+        <v>0.4055105618710598</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3531043004517882</v>
+        <v>0.3550043004517883</v>
       </c>
       <c r="C100">
-        <v>-204.3439937682133</v>
+        <v>-210.2745788349172</v>
       </c>
       <c r="D100">
-        <v>216.0500062317867</v>
+        <v>214.7224211650827</v>
       </c>
       <c r="E100">
-        <v>263.694</v>
+        <v>268.2969999999999</v>
       </c>
       <c r="F100">
-        <v>451.0939999999999</v>
+        <v>455.6969999999999</v>
       </c>
       <c r="G100">
         <v>30.7</v>
@@ -9487,37 +9487,37 @@
         <v>43.13333333333333</v>
       </c>
       <c r="M100">
-        <v>106.3679652</v>
+        <v>107.4533526</v>
       </c>
       <c r="N100">
-        <v>-63.23463186666665</v>
+        <v>-64.32001926666666</v>
       </c>
       <c r="O100">
-        <v>-3.477904752666666</v>
+        <v>-3.537601059666666</v>
       </c>
       <c r="P100">
-        <v>-59.75672711399999</v>
+        <v>-60.782418207</v>
       </c>
       <c r="Q100">
-        <v>-48.35672711399999</v>
+        <v>-49.382418207</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.35870927995779</v>
+        <v>12.67161855991558</v>
       </c>
       <c r="T100">
-        <v>48.52998443242091</v>
+        <v>97.05996886484184</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02230308090290829</v>
+        <v>0.02207779725742437</v>
       </c>
       <c r="W100">
-        <v>0.2305409335230942</v>
+        <v>0.2305940554066994</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4055105618710598</v>
+        <v>0.4014144955895339</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3550043004517883</v>
-      </c>
-      <c r="C101">
-        <v>-210.2745788349172</v>
-      </c>
-      <c r="D101">
-        <v>214.7224211650827</v>
-      </c>
-      <c r="E101">
-        <v>268.2969999999999</v>
-      </c>
-      <c r="F101">
-        <v>455.6969999999999</v>
-      </c>
-      <c r="G101">
-        <v>30.7</v>
-      </c>
-      <c r="H101">
-        <v>272.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>54.53333333333333</v>
-      </c>
-      <c r="K101">
-        <v>11.4</v>
-      </c>
-      <c r="L101">
-        <v>43.13333333333333</v>
-      </c>
-      <c r="M101">
-        <v>107.4533526</v>
-      </c>
-      <c r="N101">
-        <v>-64.32001926666666</v>
-      </c>
-      <c r="O101">
-        <v>-3.537601059666666</v>
-      </c>
-      <c r="P101">
-        <v>-60.782418207</v>
-      </c>
-      <c r="Q101">
-        <v>-49.382418207</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.67161855991558</v>
-      </c>
-      <c r="T101">
-        <v>97.05996886484184</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02207779725742437</v>
-      </c>
-      <c r="W101">
-        <v>0.2305940554066994</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4014144955895339</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
